--- a/Data source/MDSCHEMA_MEASURES.xlsx
+++ b/Data source/MDSCHEMA_MEASURES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ksoszka-my.sharepoint.com/personal/kamil_soszka_ksoszka_onmicrosoft_com/Documents/Kamil Soszka Business Intelligence/Data source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_0A58AA8DC5968491FEE2F83541FAF4E910248E6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ACD6C98-6E45-4FA4-A7E8-E25394CB7B61}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_0A58AA8DC5968491FEE2F83541C234690B948F6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6CDE2FF-C283-41A4-A97F-F4A81FA96BCA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
     <t>DEFAULT_FORMAT_STRING</t>
   </si>
   <si>
-    <t>05e709d3-5a89-4dcd-ab42-0baed2dacf98</t>
+    <t>8de6c40d-5f50-4c8f-b534-577974c93108</t>
   </si>
   <si>
     <t>Model</t>
@@ -2638,7 +2638,7 @@
         SELECTEDVALUE ( Slicer_Table[__measure] ) = "__units_sold", "Units sold"
     )
 RETURN
-    SELECTEDVALUE ( Selected_Months[Value] ) &amp; " Month Moving Average for " &amp; __selected</t>
+    SELECTEDVALUE ( Selected_Months[Value] ) &amp; " Month Moving average for " &amp; __selected</t>
   </si>
   <si>
     <t>__experience_in_pbi</t>
@@ -3954,27 +3954,27 @@
   <dimension ref="A1:U192"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="77.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="52.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="68.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
@@ -4592,7 +4592,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -5357,7 +5357,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -5663,7 +5663,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>21</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>21</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>21</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>21</v>
       </c>
@@ -7087,7 +7087,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -7240,7 +7240,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>21</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>21</v>
       </c>
@@ -7546,7 +7546,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -7749,7 +7749,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="81" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>21</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>21</v>
       </c>
@@ -8358,7 +8358,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="87" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>21</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>21</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="93" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>21</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="96" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>21</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="99" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>21</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>21</v>
       </c>
@@ -9276,7 +9276,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="105" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>21</v>
       </c>
@@ -9479,7 +9479,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>21</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="115" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>21</v>
       </c>
@@ -9935,7 +9935,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="118" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>21</v>
       </c>
@@ -10088,7 +10088,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="121" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>21</v>
       </c>
@@ -10241,7 +10241,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="124" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>21</v>
       </c>
@@ -10394,7 +10394,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="127" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>21</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>21</v>
       </c>
@@ -10700,7 +10700,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="133" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>21</v>
       </c>
@@ -10853,7 +10853,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>21</v>
       </c>
@@ -11006,7 +11006,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="139" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>21</v>
       </c>
@@ -11209,7 +11209,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="143" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>21</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="149" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>21</v>
       </c>
@@ -11665,7 +11665,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="152" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>21</v>
       </c>
@@ -11818,7 +11818,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="155" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>21</v>
       </c>
@@ -11971,7 +11971,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="158" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>21</v>
       </c>
@@ -12124,7 +12124,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="161" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>21</v>
       </c>
@@ -12277,7 +12277,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="164" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>21</v>
       </c>
@@ -12430,7 +12430,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="167" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>21</v>
       </c>
@@ -12583,7 +12583,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="170" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>21</v>
       </c>
@@ -12736,7 +12736,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="173" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>21</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="177" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>21</v>
       </c>
@@ -13042,7 +13042,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="179" spans="1:21" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>21</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="183" spans="1:21" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>21</v>
       </c>
@@ -13651,7 +13651,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="191" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>21</v>
       </c>

--- a/Data source/MDSCHEMA_MEASURES.xlsx
+++ b/Data source/MDSCHEMA_MEASURES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ksoszka-my.sharepoint.com/personal/kamil_soszka_ksoszka_onmicrosoft_com/Documents/Kamil Soszka Business Intelligence/Data source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_0A58AA8DC5968491FEE2F86EC14238E614E935E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B2E2576-775C-4E85-85E4-E1A5D4098E37}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_0A58AA8DC5968491FEE2F8C6E90ADB510A9F2A16" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{646867E9-910E-483B-A074-5FD4B1B3DA62}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Query1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Query1!$A$1:$U$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Query1!$A$1:$U$207</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="683">
   <si>
     <t>CATALOG_NAME</t>
   </si>
@@ -88,7 +88,7 @@
     <t>DEFAULT_FORMAT_STRING</t>
   </si>
   <si>
-    <t>561ff6f3-d6fc-42e4-b633-128313d80b92</t>
+    <t>b8ff92da-95d5-43b5-ab54-707ffae4b929</t>
   </si>
   <si>
     <t>Model</t>
@@ -121,7 +121,7 @@
     <t>Model_Measures</t>
   </si>
   <si>
-    <t>#,0.00</t>
+    <t>#,##0;(#,##0)</t>
   </si>
   <si>
     <t>__profit</t>
@@ -2059,6 +2059,9 @@
     <t>Time intelligence\Moving annual growth\__sales</t>
   </si>
   <si>
+    <t>$ #,##0</t>
+  </si>
+  <si>
     <t>PYMAT __sales</t>
   </si>
   <si>
@@ -2661,62 +2664,6 @@
     )
 RETURN
     Result</t>
-  </si>
-  <si>
-    <t>__rt%-(product)</t>
-  </si>
-  <si>
-    <t>[Measures].[__rt%-(product)]</t>
-  </si>
-  <si>
-    <t>DIVIDE ( [__running_total-(product)], CALCULATE ( [__profit], ALLSELECTED () ) )</t>
-  </si>
-  <si>
-    <t>0.00%;-0.00%;0.00%</t>
-  </si>
-  <si>
-    <t>__running_total-(product)</t>
-  </si>
-  <si>
-    <t>[Measures].[__running_total-(product)]</t>
-  </si>
-  <si>
-    <t>CALCULATE (
-    [__profit],
-    FILTER (
-        ALLSELECTED ( 'financials (web)'[Product] ),
-        ISONORAFTER (
-            'financials (web)'[Product], MAX ( 'financials (web)'[Product] ), DESC
-        )
-    )
-)</t>
-  </si>
-  <si>
-    <t>__running_total</t>
-  </si>
-  <si>
-    <t>[Measures].[__running_total]</t>
-  </si>
-  <si>
-    <t>VAR MaxDate =
-    MAX ( 'Date'[Date] ) -- Saves the last visible date
-RETURN
-    CALCULATE (
-        [__profit],
-        -- Computes sales amount
-        'Date'[Date] &lt;= MaxDate,
-        -- Where date is before the last visible date
-        ALL ( 'Date' ) -- Removes any other filters from Date
-    )</t>
-  </si>
-  <si>
-    <t>__rt%</t>
-  </si>
-  <si>
-    <t>[Measures].[__rt%]</t>
-  </si>
-  <si>
-    <t>DIVIDE ( [__running_total], CALCULATE ( [__profit], ALLSELECTED () ) )</t>
   </si>
   <si>
     <t>DumpFilters</t>
@@ -3528,7 +3475,7 @@
     <t>[Measures].[formatted cogs]</t>
   </si>
   <si>
-    <t>FORMAT ( [__cogs], "$ #,,#, K" )</t>
+    <t>FORMAT ( [__cogs], "#,,#" )</t>
   </si>
   <si>
     <t>KPI Cards</t>
@@ -3540,7 +3487,7 @@
     <t>[Measures].[formatted discounts]</t>
   </si>
   <si>
-    <t>FORMAT ( [__discounts], "$ #,,#, K" )</t>
+    <t>FORMAT ( [__discounts], "#,,#" )</t>
   </si>
   <si>
     <t>formatted gross_sales</t>
@@ -3549,7 +3496,7 @@
     <t>[Measures].[formatted gross_sales]</t>
   </si>
   <si>
-    <t>FORMAT ( [__gross_sales], "$ #,,#, K" )</t>
+    <t>FORMAT ( [__gross_sales], "#,,#" )</t>
   </si>
   <si>
     <t>formatted profit</t>
@@ -3558,7 +3505,7 @@
     <t>[Measures].[formatted profit]</t>
   </si>
   <si>
-    <t>FORMAT ( [__profit], "$ #,,#, K" )</t>
+    <t>FORMAT ( [__profit], "#,,#" )</t>
   </si>
   <si>
     <t>formatted sales</t>
@@ -3567,7 +3514,7 @@
     <t>[Measures].[formatted sales]</t>
   </si>
   <si>
-    <t>FORMAT ( [__sales], "$ #,,#, K" )</t>
+    <t>FORMAT ( [__sales], "#,,#" )</t>
   </si>
   <si>
     <t>mom% | mom (sales)</t>
@@ -3577,7 +3524,7 @@
   </si>
   <si>
     <t>FORMAT ( [MOMTD % __sales], "0.0%" ) &amp; " | "
-    &amp; FORMAT ( [MOM __sales], "$ #,,#, K" )</t>
+    &amp; FORMAT ( [MOM __sales], "#,,#" )</t>
   </si>
   <si>
     <t>mom% | mom (cogs)</t>
@@ -3587,7 +3534,7 @@
   </si>
   <si>
     <t>FORMAT ( [MOMTD % __cogs], "0.0%" ) &amp; " | "
-    &amp; FORMAT ( [MOM __cogs], "$ #,,#, K" )</t>
+    &amp; FORMAT ( [MOM __cogs], "#,,#" )</t>
   </si>
   <si>
     <t>mom% | mom (discounts)</t>
@@ -3605,7 +3552,7 @@
 ) &amp; " | "
     &amp; FORMAT (
         [__discounts] - CALCULATE ( [__discounts], DATEADD ( 'Date'[Date], -1, MONTH ) ),
-        "$ #,,#, K"
+        "#,,#K"
     )</t>
   </si>
   <si>
@@ -3616,7 +3563,7 @@
   </si>
   <si>
     <t>FORMAT ( [MOMTD % __gross_sales], "0.0%" ) &amp; " | "
-    &amp; FORMAT ( [MOM __gross_sales], "$ #,,#, K" )</t>
+    &amp; FORMAT ( [MOM __gross_sales], "#,,#" )</t>
   </si>
   <si>
     <t>mom% | mom (profit)</t>
@@ -3626,7 +3573,7 @@
   </si>
   <si>
     <t>FORMAT ( [MOMTD % __profit], "0.0%" ) &amp; " | "
-    &amp; FORMAT ( [MOM __profit], "$ #,,#, K" )</t>
+    &amp; FORMAT ( [MOM __profit], "#,,#" )</t>
   </si>
   <si>
     <t>mom% color (sales)</t>
@@ -3658,7 +3605,7 @@
     DIVIDE (
         [__discounts],
         CALCULATE ( [__discounts], DATEADD ( 'Date'[Date], -1, MONTH ) )
-    ) - 1 &gt; 0, "Green",
+    ) - 1 &lt; 0, "Green",
     "Red"
 )</t>
   </si>
@@ -3679,6 +3626,27 @@
   </si>
   <si>
     <t>SWITCH ( TRUE (), [MOM % __profit] &gt; 0, "Green", "Red" )</t>
+  </si>
+  <si>
+    <t>__line_chart</t>
+  </si>
+  <si>
+    <t>[Measures].[__line_chart]</t>
+  </si>
+  <si>
+    <t>VAR __highest =
+    MAXX ( ALLSELECTED ( 'Date'[Date] ), [__profit] )
+VAR __lowest =
+    MINX ( ALLSELECTED ( 'Date'[Date] ), [__profit] )
+VAR Result =
+    SWITCH (
+        TRUE (),
+        [__profit] = __highest, [__profit],
+        [__profit] = __lowest, [__profit],
+        BLANK ()
+    )
+RETURN
+    Result</t>
   </si>
   <si>
     <t>_ShowValueForDates</t>
@@ -3726,6 +3694,57 @@
   </si>
   <si>
     <t>Slicer_Table</t>
+  </si>
+  <si>
+    <t>Group 1</t>
+  </si>
+  <si>
+    <t>[Measures].[Group 1]</t>
+  </si>
+  <si>
+    <t>VAR Result =
+    SWITCH (
+        TRUE (),
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__cogs", [__cogs],
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__gross_sales", [__gross_sales],
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__profit", [__profit],
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__sales", [__sales],
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__units_sold", [__units_sold],
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__discounts", SUM ( 'financials (web)'[Discounts] )
+    )
+RETURN
+    IF (
+        MAX ( 'Multi Measure Table'[Measure group] ) = "Measure group 1",
+        Result,
+        BLANK ()
+    )</t>
+  </si>
+  <si>
+    <t>Multi Measure Table</t>
+  </si>
+  <si>
+    <t>Group 2</t>
+  </si>
+  <si>
+    <t>[Measures].[Group 2]</t>
+  </si>
+  <si>
+    <t>VAR Result =
+    SWITCH (
+        TRUE (),
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__cogs", [__cogs],
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__gross_sales", [__gross_sales],
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__profit", [__profit],
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__sales", [__sales],
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__units_sold", [__units_sold],
+        SELECTEDVALUE ( 'Multi Measure Table'[Value2] ) = "__discounts", SUM ( 'financials (web)'[Discounts] )
+    )
+RETURN
+    IF (
+        MAX ( 'Multi Measure Table'[Measure group] ) = "Measure group 2",
+        Result,
+        BLANK ()
+    )</t>
   </si>
   <si>
     <t>__Default measure</t>
@@ -4122,10 +4141,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U208"/>
+  <dimension ref="A1:U207"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.21875" bestFit="1" customWidth="1"/>
@@ -4627,6 +4646,9 @@
       <c r="T9" t="s">
         <v>55</v>
       </c>
+      <c r="U9" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -4677,6 +4699,9 @@
       <c r="T10" t="s">
         <v>55</v>
       </c>
+      <c r="U10" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -4727,6 +4752,9 @@
       <c r="T11" t="s">
         <v>55</v>
       </c>
+      <c r="U11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="12" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -4777,6 +4805,9 @@
       <c r="T12" t="s">
         <v>65</v>
       </c>
+      <c r="U12" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="13" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -4827,6 +4858,9 @@
       <c r="T13" t="s">
         <v>65</v>
       </c>
+      <c r="U13" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -4930,6 +4964,9 @@
       <c r="T15" t="s">
         <v>65</v>
       </c>
+      <c r="U15" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="16" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -4980,6 +5017,9 @@
       <c r="T16" t="s">
         <v>65</v>
       </c>
+      <c r="U16" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -5083,6 +5123,9 @@
       <c r="T18" t="s">
         <v>65</v>
       </c>
+      <c r="U18" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="19" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -5133,6 +5176,9 @@
       <c r="T19" t="s">
         <v>65</v>
       </c>
+      <c r="U19" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -5236,6 +5282,9 @@
       <c r="T21" t="s">
         <v>94</v>
       </c>
+      <c r="U21" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -5286,6 +5335,9 @@
       <c r="T22" t="s">
         <v>94</v>
       </c>
+      <c r="U22" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -5389,6 +5441,9 @@
       <c r="T24" t="s">
         <v>94</v>
       </c>
+      <c r="U24" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="25" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -5439,6 +5494,9 @@
       <c r="T25" t="s">
         <v>94</v>
       </c>
+      <c r="U25" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -5542,6 +5600,9 @@
       <c r="T27" t="s">
         <v>94</v>
       </c>
+      <c r="U27" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="28" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -5592,6 +5653,9 @@
       <c r="T28" t="s">
         <v>94</v>
       </c>
+      <c r="U28" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -5695,6 +5759,9 @@
       <c r="T30" t="s">
         <v>122</v>
       </c>
+      <c r="U30" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="31" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -5745,6 +5812,9 @@
       <c r="T31" t="s">
         <v>122</v>
       </c>
+      <c r="U31" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -5848,6 +5918,9 @@
       <c r="T33" t="s">
         <v>122</v>
       </c>
+      <c r="U33" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="34" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -5898,6 +5971,9 @@
       <c r="T34" t="s">
         <v>122</v>
       </c>
+      <c r="U34" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
@@ -6001,6 +6077,9 @@
       <c r="T36" t="s">
         <v>122</v>
       </c>
+      <c r="U36" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="37" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -6051,6 +6130,9 @@
       <c r="T37" t="s">
         <v>122</v>
       </c>
+      <c r="U37" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -6154,6 +6236,9 @@
       <c r="T39" t="s">
         <v>150</v>
       </c>
+      <c r="U39" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="40" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -6204,6 +6289,9 @@
       <c r="T40" t="s">
         <v>150</v>
       </c>
+      <c r="U40" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="41" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -6254,6 +6342,9 @@
       <c r="T41" t="s">
         <v>150</v>
       </c>
+      <c r="U41" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -6357,6 +6448,9 @@
       <c r="T43" t="s">
         <v>163</v>
       </c>
+      <c r="U43" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="44" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -6407,6 +6501,9 @@
       <c r="T44" t="s">
         <v>163</v>
       </c>
+      <c r="U44" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="45" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -6457,6 +6554,9 @@
       <c r="T45" t="s">
         <v>163</v>
       </c>
+      <c r="U45" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="46" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -6507,6 +6607,9 @@
       <c r="T46" t="s">
         <v>173</v>
       </c>
+      <c r="U46" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="47" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -6557,6 +6660,9 @@
       <c r="T47" t="s">
         <v>173</v>
       </c>
+      <c r="U47" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -6660,6 +6766,9 @@
       <c r="T49" t="s">
         <v>173</v>
       </c>
+      <c r="U49" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="50" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -6710,6 +6819,9 @@
       <c r="T50" t="s">
         <v>173</v>
       </c>
+      <c r="U50" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -6813,6 +6925,9 @@
       <c r="T52" t="s">
         <v>173</v>
       </c>
+      <c r="U52" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="53" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -6863,6 +6978,9 @@
       <c r="T53" t="s">
         <v>173</v>
       </c>
+      <c r="U53" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -6966,6 +7084,9 @@
       <c r="T55" t="s">
         <v>201</v>
       </c>
+      <c r="U55" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="56" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -7016,6 +7137,9 @@
       <c r="T56" t="s">
         <v>201</v>
       </c>
+      <c r="U56" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -7119,6 +7243,9 @@
       <c r="T58" t="s">
         <v>201</v>
       </c>
+      <c r="U58" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="59" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -7169,6 +7296,9 @@
       <c r="T59" t="s">
         <v>201</v>
       </c>
+      <c r="U59" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -7272,6 +7402,9 @@
       <c r="T61" t="s">
         <v>201</v>
       </c>
+      <c r="U61" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="62" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -7322,6 +7455,9 @@
       <c r="T62" t="s">
         <v>201</v>
       </c>
+      <c r="U62" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
@@ -7425,6 +7561,9 @@
       <c r="T64" t="s">
         <v>229</v>
       </c>
+      <c r="U64" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="65" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -7475,6 +7614,9 @@
       <c r="T65" t="s">
         <v>229</v>
       </c>
+      <c r="U65" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -7578,6 +7720,9 @@
       <c r="T67" t="s">
         <v>229</v>
       </c>
+      <c r="U67" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="68" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -7628,6 +7773,9 @@
       <c r="T68" t="s">
         <v>229</v>
       </c>
+      <c r="U68" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -7731,6 +7879,9 @@
       <c r="T70" t="s">
         <v>229</v>
       </c>
+      <c r="U70" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="71" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -7781,6 +7932,9 @@
       <c r="T71" t="s">
         <v>229</v>
       </c>
+      <c r="U71" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -7884,6 +8038,9 @@
       <c r="T73" t="s">
         <v>257</v>
       </c>
+      <c r="U73" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="74" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -7934,6 +8091,9 @@
       <c r="T74" t="s">
         <v>257</v>
       </c>
+      <c r="U74" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="75" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
@@ -7984,6 +8144,9 @@
       <c r="T75" t="s">
         <v>257</v>
       </c>
+      <c r="U75" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -8087,6 +8250,9 @@
       <c r="T77" t="s">
         <v>270</v>
       </c>
+      <c r="U77" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -8137,6 +8303,9 @@
       <c r="T78" t="s">
         <v>270</v>
       </c>
+      <c r="U78" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
@@ -8187,6 +8356,9 @@
       <c r="T79" t="s">
         <v>270</v>
       </c>
+      <c r="U79" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="80" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
@@ -8237,6 +8409,9 @@
       <c r="T80" t="s">
         <v>280</v>
       </c>
+      <c r="U80" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="81" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
@@ -8287,6 +8462,9 @@
       <c r="T81" t="s">
         <v>280</v>
       </c>
+      <c r="U81" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
@@ -8390,6 +8568,9 @@
       <c r="T83" t="s">
         <v>280</v>
       </c>
+      <c r="U83" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="84" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
@@ -8440,6 +8621,9 @@
       <c r="T84" t="s">
         <v>280</v>
       </c>
+      <c r="U84" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
@@ -8543,6 +8727,9 @@
       <c r="T86" t="s">
         <v>280</v>
       </c>
+      <c r="U86" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="87" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
@@ -8593,6 +8780,9 @@
       <c r="T87" t="s">
         <v>280</v>
       </c>
+      <c r="U87" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
@@ -8696,6 +8886,9 @@
       <c r="T89" t="s">
         <v>308</v>
       </c>
+      <c r="U89" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="90" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
@@ -8746,6 +8939,9 @@
       <c r="T90" t="s">
         <v>308</v>
       </c>
+      <c r="U90" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
@@ -8849,6 +9045,9 @@
       <c r="T92" t="s">
         <v>308</v>
       </c>
+      <c r="U92" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="93" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
@@ -8899,6 +9098,9 @@
       <c r="T93" t="s">
         <v>308</v>
       </c>
+      <c r="U93" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
@@ -9002,6 +9204,9 @@
       <c r="T95" t="s">
         <v>308</v>
       </c>
+      <c r="U95" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="96" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -9052,6 +9257,9 @@
       <c r="T96" t="s">
         <v>308</v>
       </c>
+      <c r="U96" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
@@ -9155,6 +9363,9 @@
       <c r="T98" t="s">
         <v>336</v>
       </c>
+      <c r="U98" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="99" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
@@ -9205,6 +9416,9 @@
       <c r="T99" t="s">
         <v>336</v>
       </c>
+      <c r="U99" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
@@ -9308,6 +9522,9 @@
       <c r="T101" t="s">
         <v>336</v>
       </c>
+      <c r="U101" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="102" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
@@ -9358,6 +9575,9 @@
       <c r="T102" t="s">
         <v>336</v>
       </c>
+      <c r="U102" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
@@ -9461,6 +9681,9 @@
       <c r="T104" t="s">
         <v>336</v>
       </c>
+      <c r="U104" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="105" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
@@ -9511,6 +9734,9 @@
       <c r="T105" t="s">
         <v>336</v>
       </c>
+      <c r="U105" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
@@ -9614,6 +9840,9 @@
       <c r="T107" t="s">
         <v>364</v>
       </c>
+      <c r="U107" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="108" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -9664,6 +9893,9 @@
       <c r="T108" t="s">
         <v>364</v>
       </c>
+      <c r="U108" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="109" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
@@ -9714,6 +9946,9 @@
       <c r="T109" t="s">
         <v>364</v>
       </c>
+      <c r="U109" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
@@ -9817,6 +10052,9 @@
       <c r="T111" t="s">
         <v>377</v>
       </c>
+      <c r="U111" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
@@ -9867,6 +10105,9 @@
       <c r="T112" t="s">
         <v>377</v>
       </c>
+      <c r="U112" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -9917,6 +10158,9 @@
       <c r="T113" t="s">
         <v>377</v>
       </c>
+      <c r="U113" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="114" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
@@ -9967,6 +10211,9 @@
       <c r="T114" t="s">
         <v>387</v>
       </c>
+      <c r="U114" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="115" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
@@ -10017,6 +10264,9 @@
       <c r="T115" t="s">
         <v>387</v>
       </c>
+      <c r="U115" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
@@ -10120,6 +10370,9 @@
       <c r="T117" t="s">
         <v>387</v>
       </c>
+      <c r="U117" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="118" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
@@ -10170,6 +10423,9 @@
       <c r="T118" t="s">
         <v>387</v>
       </c>
+      <c r="U118" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
@@ -10273,6 +10529,9 @@
       <c r="T120" t="s">
         <v>387</v>
       </c>
+      <c r="U120" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="121" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
@@ -10323,6 +10582,9 @@
       <c r="T121" t="s">
         <v>387</v>
       </c>
+      <c r="U121" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
@@ -10426,6 +10688,9 @@
       <c r="T123" t="s">
         <v>415</v>
       </c>
+      <c r="U123" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="124" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
@@ -10476,6 +10741,9 @@
       <c r="T124" t="s">
         <v>415</v>
       </c>
+      <c r="U124" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
@@ -10579,6 +10847,9 @@
       <c r="T126" t="s">
         <v>415</v>
       </c>
+      <c r="U126" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="127" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
@@ -10629,6 +10900,9 @@
       <c r="T127" t="s">
         <v>415</v>
       </c>
+      <c r="U127" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
@@ -10732,6 +11006,9 @@
       <c r="T129" t="s">
         <v>415</v>
       </c>
+      <c r="U129" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="130" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
@@ -10782,6 +11059,9 @@
       <c r="T130" t="s">
         <v>415</v>
       </c>
+      <c r="U130" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
@@ -10885,6 +11165,9 @@
       <c r="T132" t="s">
         <v>443</v>
       </c>
+      <c r="U132" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="133" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
@@ -10935,6 +11218,9 @@
       <c r="T133" t="s">
         <v>443</v>
       </c>
+      <c r="U133" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
@@ -11038,6 +11324,9 @@
       <c r="T135" t="s">
         <v>443</v>
       </c>
+      <c r="U135" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="136" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
@@ -11088,6 +11377,9 @@
       <c r="T136" t="s">
         <v>443</v>
       </c>
+      <c r="U136" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
@@ -11191,6 +11483,9 @@
       <c r="T138" t="s">
         <v>443</v>
       </c>
+      <c r="U138" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="139" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
@@ -11241,6 +11536,9 @@
       <c r="T139" t="s">
         <v>443</v>
       </c>
+      <c r="U139" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
@@ -11344,6 +11642,9 @@
       <c r="T141" t="s">
         <v>471</v>
       </c>
+      <c r="U141" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="142" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
@@ -11353,14 +11654,14 @@
         <v>22</v>
       </c>
       <c r="D142" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E142" t="s">
+        <v>474</v>
+      </c>
+      <c r="F142" t="s">
         <v>473</v>
       </c>
-      <c r="F142" t="s">
-        <v>472</v>
-      </c>
       <c r="H142">
         <v>0</v>
       </c>
@@ -11377,16 +11678,16 @@
         <v>28</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O142" t="s">
         <v>30</v>
       </c>
       <c r="Q142" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="R142" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="S142" t="s">
         <v>31</v>
@@ -11394,6 +11695,9 @@
       <c r="T142" t="s">
         <v>471</v>
       </c>
+      <c r="U142" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="143" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
@@ -11403,14 +11707,14 @@
         <v>22</v>
       </c>
       <c r="D143" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E143" t="s">
+        <v>477</v>
+      </c>
+      <c r="F143" t="s">
         <v>476</v>
       </c>
-      <c r="F143" t="s">
-        <v>475</v>
-      </c>
       <c r="H143">
         <v>0</v>
       </c>
@@ -11427,16 +11731,16 @@
         <v>28</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O143" t="s">
         <v>30</v>
       </c>
       <c r="Q143" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R143" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="S143" t="s">
         <v>31</v>
@@ -11444,6 +11748,9 @@
       <c r="T143" t="s">
         <v>471</v>
       </c>
+      <c r="U143" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
@@ -11453,14 +11760,14 @@
         <v>22</v>
       </c>
       <c r="D144" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E144" t="s">
+        <v>480</v>
+      </c>
+      <c r="F144" t="s">
         <v>479</v>
       </c>
-      <c r="F144" t="s">
-        <v>478</v>
-      </c>
       <c r="H144">
         <v>0</v>
       </c>
@@ -11477,16 +11784,16 @@
         <v>28</v>
       </c>
       <c r="N144" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O144" t="s">
         <v>30</v>
       </c>
       <c r="Q144" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="R144" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="S144" t="s">
         <v>31</v>
@@ -11506,14 +11813,14 @@
         <v>22</v>
       </c>
       <c r="D145" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E145" t="s">
+        <v>483</v>
+      </c>
+      <c r="F145" t="s">
         <v>482</v>
       </c>
-      <c r="F145" t="s">
-        <v>481</v>
-      </c>
       <c r="H145">
         <v>0</v>
       </c>
@@ -11530,22 +11837,25 @@
         <v>28</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O145" t="s">
         <v>30</v>
       </c>
       <c r="Q145" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="R145" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="S145" t="s">
         <v>31</v>
       </c>
       <c r="T145" t="s">
-        <v>484</v>
+        <v>485</v>
+      </c>
+      <c r="U145" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="146" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
@@ -11556,46 +11866,49 @@
         <v>22</v>
       </c>
       <c r="D146" t="s">
+        <v>486</v>
+      </c>
+      <c r="E146" t="s">
+        <v>487</v>
+      </c>
+      <c r="F146" t="s">
+        <v>486</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146" t="s">
+        <v>25</v>
+      </c>
+      <c r="J146" t="s">
+        <v>26</v>
+      </c>
+      <c r="K146" t="s">
+        <v>27</v>
+      </c>
+      <c r="M146" t="s">
+        <v>28</v>
+      </c>
+      <c r="N146" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="O146" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>486</v>
+      </c>
+      <c r="R146" t="s">
+        <v>486</v>
+      </c>
+      <c r="S146" t="s">
+        <v>31</v>
+      </c>
+      <c r="T146" t="s">
         <v>485</v>
       </c>
-      <c r="E146" t="s">
-        <v>486</v>
-      </c>
-      <c r="F146" t="s">
-        <v>485</v>
-      </c>
-      <c r="H146">
-        <v>0</v>
-      </c>
-      <c r="I146" t="s">
-        <v>25</v>
-      </c>
-      <c r="J146" t="s">
-        <v>26</v>
-      </c>
-      <c r="K146" t="s">
-        <v>27</v>
-      </c>
-      <c r="M146" t="s">
-        <v>28</v>
-      </c>
-      <c r="N146" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="O146" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q146" t="s">
-        <v>485</v>
-      </c>
-      <c r="R146" t="s">
-        <v>485</v>
-      </c>
-      <c r="S146" t="s">
-        <v>31</v>
-      </c>
-      <c r="T146" t="s">
-        <v>484</v>
+      <c r="U146" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="147" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
@@ -11606,14 +11919,14 @@
         <v>22</v>
       </c>
       <c r="D147" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E147" t="s">
+        <v>490</v>
+      </c>
+      <c r="F147" t="s">
         <v>489</v>
       </c>
-      <c r="F147" t="s">
-        <v>488</v>
-      </c>
       <c r="H147">
         <v>0</v>
       </c>
@@ -11630,22 +11943,25 @@
         <v>28</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O147" t="s">
         <v>30</v>
       </c>
       <c r="Q147" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="R147" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="S147" t="s">
         <v>31</v>
       </c>
       <c r="T147" t="s">
-        <v>484</v>
+        <v>485</v>
+      </c>
+      <c r="U147" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="148" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -11656,14 +11972,14 @@
         <v>22</v>
       </c>
       <c r="D148" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E148" t="s">
+        <v>493</v>
+      </c>
+      <c r="F148" t="s">
         <v>492</v>
       </c>
-      <c r="F148" t="s">
-        <v>491</v>
-      </c>
       <c r="H148">
         <v>0</v>
       </c>
@@ -11680,22 +11996,25 @@
         <v>28</v>
       </c>
       <c r="N148" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O148" t="s">
         <v>30</v>
       </c>
       <c r="Q148" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="R148" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="S148" t="s">
         <v>31</v>
       </c>
       <c r="T148" t="s">
-        <v>494</v>
+        <v>495</v>
+      </c>
+      <c r="U148" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="149" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -11706,46 +12025,49 @@
         <v>22</v>
       </c>
       <c r="D149" t="s">
+        <v>496</v>
+      </c>
+      <c r="E149" t="s">
+        <v>497</v>
+      </c>
+      <c r="F149" t="s">
+        <v>496</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149" t="s">
+        <v>25</v>
+      </c>
+      <c r="J149" t="s">
+        <v>26</v>
+      </c>
+      <c r="K149" t="s">
+        <v>27</v>
+      </c>
+      <c r="M149" t="s">
+        <v>28</v>
+      </c>
+      <c r="N149" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="O149" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>496</v>
+      </c>
+      <c r="R149" t="s">
+        <v>496</v>
+      </c>
+      <c r="S149" t="s">
+        <v>31</v>
+      </c>
+      <c r="T149" t="s">
         <v>495</v>
       </c>
-      <c r="E149" t="s">
-        <v>496</v>
-      </c>
-      <c r="F149" t="s">
-        <v>495</v>
-      </c>
-      <c r="H149">
-        <v>0</v>
-      </c>
-      <c r="I149" t="s">
-        <v>25</v>
-      </c>
-      <c r="J149" t="s">
-        <v>26</v>
-      </c>
-      <c r="K149" t="s">
-        <v>27</v>
-      </c>
-      <c r="M149" t="s">
-        <v>28</v>
-      </c>
-      <c r="N149" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="O149" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q149" t="s">
-        <v>495</v>
-      </c>
-      <c r="R149" t="s">
-        <v>495</v>
-      </c>
-      <c r="S149" t="s">
-        <v>31</v>
-      </c>
-      <c r="T149" t="s">
-        <v>494</v>
+      <c r="U149" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.3">
@@ -11756,14 +12078,14 @@
         <v>22</v>
       </c>
       <c r="D150" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E150" t="s">
+        <v>500</v>
+      </c>
+      <c r="F150" t="s">
         <v>499</v>
       </c>
-      <c r="F150" t="s">
-        <v>498</v>
-      </c>
       <c r="H150">
         <v>0</v>
       </c>
@@ -11780,22 +12102,22 @@
         <v>28</v>
       </c>
       <c r="N150" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O150" t="s">
         <v>30</v>
       </c>
       <c r="Q150" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="R150" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="S150" t="s">
         <v>31</v>
       </c>
       <c r="T150" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="U150" t="s">
         <v>72</v>
@@ -11809,14 +12131,14 @@
         <v>22</v>
       </c>
       <c r="D151" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E151" t="s">
+        <v>503</v>
+      </c>
+      <c r="F151" t="s">
         <v>502</v>
       </c>
-      <c r="F151" t="s">
-        <v>501</v>
-      </c>
       <c r="H151">
         <v>0</v>
       </c>
@@ -11833,22 +12155,25 @@
         <v>28</v>
       </c>
       <c r="N151" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O151" t="s">
         <v>30</v>
       </c>
       <c r="Q151" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="R151" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="S151" t="s">
         <v>31</v>
       </c>
       <c r="T151" t="s">
-        <v>494</v>
+        <v>495</v>
+      </c>
+      <c r="U151" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="152" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -11859,14 +12184,14 @@
         <v>22</v>
       </c>
       <c r="D152" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E152" t="s">
+        <v>506</v>
+      </c>
+      <c r="F152" t="s">
         <v>505</v>
       </c>
-      <c r="F152" t="s">
-        <v>504</v>
-      </c>
       <c r="H152">
         <v>0</v>
       </c>
@@ -11883,22 +12208,25 @@
         <v>28</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O152" t="s">
         <v>30</v>
       </c>
       <c r="Q152" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="R152" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="S152" t="s">
         <v>31</v>
       </c>
       <c r="T152" t="s">
-        <v>494</v>
+        <v>495</v>
+      </c>
+      <c r="U152" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.3">
@@ -11909,14 +12237,14 @@
         <v>22</v>
       </c>
       <c r="D153" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E153" t="s">
+        <v>509</v>
+      </c>
+      <c r="F153" t="s">
         <v>508</v>
       </c>
-      <c r="F153" t="s">
-        <v>507</v>
-      </c>
       <c r="H153">
         <v>0</v>
       </c>
@@ -11933,22 +12261,22 @@
         <v>28</v>
       </c>
       <c r="N153" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O153" t="s">
         <v>30</v>
       </c>
       <c r="Q153" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="R153" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="S153" t="s">
         <v>31</v>
       </c>
       <c r="T153" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="U153" t="s">
         <v>72</v>
@@ -11962,14 +12290,14 @@
         <v>22</v>
       </c>
       <c r="D154" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E154" t="s">
+        <v>512</v>
+      </c>
+      <c r="F154" t="s">
         <v>511</v>
       </c>
-      <c r="F154" t="s">
-        <v>510</v>
-      </c>
       <c r="H154">
         <v>0</v>
       </c>
@@ -11986,22 +12314,25 @@
         <v>28</v>
       </c>
       <c r="N154" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O154" t="s">
         <v>30</v>
       </c>
       <c r="Q154" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="R154" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="S154" t="s">
         <v>31</v>
       </c>
       <c r="T154" t="s">
-        <v>494</v>
+        <v>495</v>
+      </c>
+      <c r="U154" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="155" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -12012,14 +12343,14 @@
         <v>22</v>
       </c>
       <c r="D155" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E155" t="s">
+        <v>515</v>
+      </c>
+      <c r="F155" t="s">
         <v>514</v>
       </c>
-      <c r="F155" t="s">
-        <v>513</v>
-      </c>
       <c r="H155">
         <v>0</v>
       </c>
@@ -12036,22 +12367,25 @@
         <v>28</v>
       </c>
       <c r="N155" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O155" t="s">
         <v>30</v>
       </c>
       <c r="Q155" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="R155" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="S155" t="s">
         <v>31</v>
       </c>
       <c r="T155" t="s">
-        <v>494</v>
+        <v>495</v>
+      </c>
+      <c r="U155" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.3">
@@ -12062,14 +12396,14 @@
         <v>22</v>
       </c>
       <c r="D156" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E156" t="s">
+        <v>518</v>
+      </c>
+      <c r="F156" t="s">
         <v>517</v>
       </c>
-      <c r="F156" t="s">
-        <v>516</v>
-      </c>
       <c r="H156">
         <v>0</v>
       </c>
@@ -12086,22 +12420,22 @@
         <v>28</v>
       </c>
       <c r="N156" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O156" t="s">
         <v>30</v>
       </c>
       <c r="Q156" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="R156" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="S156" t="s">
         <v>31</v>
       </c>
       <c r="T156" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="U156" t="s">
         <v>72</v>
@@ -12115,14 +12449,14 @@
         <v>22</v>
       </c>
       <c r="D157" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E157" t="s">
+        <v>521</v>
+      </c>
+      <c r="F157" t="s">
         <v>520</v>
       </c>
-      <c r="F157" t="s">
-        <v>519</v>
-      </c>
       <c r="H157">
         <v>0</v>
       </c>
@@ -12139,22 +12473,25 @@
         <v>28</v>
       </c>
       <c r="N157" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O157" t="s">
         <v>30</v>
       </c>
       <c r="Q157" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="R157" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="S157" t="s">
         <v>31</v>
       </c>
       <c r="T157" t="s">
-        <v>522</v>
+        <v>523</v>
+      </c>
+      <c r="U157" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -12165,46 +12502,49 @@
         <v>22</v>
       </c>
       <c r="D158" t="s">
+        <v>524</v>
+      </c>
+      <c r="E158" t="s">
+        <v>525</v>
+      </c>
+      <c r="F158" t="s">
+        <v>524</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158" t="s">
+        <v>25</v>
+      </c>
+      <c r="J158" t="s">
+        <v>26</v>
+      </c>
+      <c r="K158" t="s">
+        <v>27</v>
+      </c>
+      <c r="M158" t="s">
+        <v>28</v>
+      </c>
+      <c r="N158" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="O158" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>524</v>
+      </c>
+      <c r="R158" t="s">
+        <v>524</v>
+      </c>
+      <c r="S158" t="s">
+        <v>31</v>
+      </c>
+      <c r="T158" t="s">
         <v>523</v>
       </c>
-      <c r="E158" t="s">
-        <v>524</v>
-      </c>
-      <c r="F158" t="s">
-        <v>523</v>
-      </c>
-      <c r="H158">
-        <v>0</v>
-      </c>
-      <c r="I158" t="s">
-        <v>25</v>
-      </c>
-      <c r="J158" t="s">
-        <v>26</v>
-      </c>
-      <c r="K158" t="s">
-        <v>27</v>
-      </c>
-      <c r="M158" t="s">
-        <v>28</v>
-      </c>
-      <c r="N158" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="O158" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q158" t="s">
-        <v>523</v>
-      </c>
-      <c r="R158" t="s">
-        <v>523</v>
-      </c>
-      <c r="S158" t="s">
-        <v>31</v>
-      </c>
-      <c r="T158" t="s">
-        <v>522</v>
+      <c r="U158" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.3">
@@ -12215,14 +12555,14 @@
         <v>22</v>
       </c>
       <c r="D159" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E159" t="s">
+        <v>528</v>
+      </c>
+      <c r="F159" t="s">
         <v>527</v>
       </c>
-      <c r="F159" t="s">
-        <v>526</v>
-      </c>
       <c r="H159">
         <v>0</v>
       </c>
@@ -12239,22 +12579,22 @@
         <v>28</v>
       </c>
       <c r="N159" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O159" t="s">
         <v>30</v>
       </c>
       <c r="Q159" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="R159" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="S159" t="s">
         <v>31</v>
       </c>
       <c r="T159" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="U159" t="s">
         <v>72</v>
@@ -12268,14 +12608,14 @@
         <v>22</v>
       </c>
       <c r="D160" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E160" t="s">
+        <v>531</v>
+      </c>
+      <c r="F160" t="s">
         <v>530</v>
       </c>
-      <c r="F160" t="s">
-        <v>529</v>
-      </c>
       <c r="H160">
         <v>0</v>
       </c>
@@ -12292,22 +12632,25 @@
         <v>28</v>
       </c>
       <c r="N160" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O160" t="s">
         <v>30</v>
       </c>
       <c r="Q160" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="R160" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="S160" t="s">
         <v>31</v>
       </c>
       <c r="T160" t="s">
-        <v>522</v>
+        <v>523</v>
+      </c>
+      <c r="U160" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="161" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -12318,14 +12661,14 @@
         <v>22</v>
       </c>
       <c r="D161" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E161" t="s">
+        <v>534</v>
+      </c>
+      <c r="F161" t="s">
         <v>533</v>
       </c>
-      <c r="F161" t="s">
-        <v>532</v>
-      </c>
       <c r="H161">
         <v>0</v>
       </c>
@@ -12342,22 +12685,25 @@
         <v>28</v>
       </c>
       <c r="N161" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O161" t="s">
         <v>30</v>
       </c>
       <c r="Q161" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="R161" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="S161" t="s">
         <v>31</v>
       </c>
       <c r="T161" t="s">
-        <v>522</v>
+        <v>523</v>
+      </c>
+      <c r="U161" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.3">
@@ -12368,14 +12714,14 @@
         <v>22</v>
       </c>
       <c r="D162" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E162" t="s">
+        <v>537</v>
+      </c>
+      <c r="F162" t="s">
         <v>536</v>
       </c>
-      <c r="F162" t="s">
-        <v>535</v>
-      </c>
       <c r="H162">
         <v>0</v>
       </c>
@@ -12392,22 +12738,22 @@
         <v>28</v>
       </c>
       <c r="N162" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O162" t="s">
         <v>30</v>
       </c>
       <c r="Q162" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="R162" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="S162" t="s">
         <v>31</v>
       </c>
       <c r="T162" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="U162" t="s">
         <v>72</v>
@@ -12421,14 +12767,14 @@
         <v>22</v>
       </c>
       <c r="D163" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E163" t="s">
+        <v>540</v>
+      </c>
+      <c r="F163" t="s">
         <v>539</v>
       </c>
-      <c r="F163" t="s">
-        <v>538</v>
-      </c>
       <c r="H163">
         <v>0</v>
       </c>
@@ -12445,22 +12791,25 @@
         <v>28</v>
       </c>
       <c r="N163" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O163" t="s">
         <v>30</v>
       </c>
       <c r="Q163" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="R163" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="S163" t="s">
         <v>31</v>
       </c>
       <c r="T163" t="s">
-        <v>522</v>
+        <v>523</v>
+      </c>
+      <c r="U163" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="164" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -12471,14 +12820,14 @@
         <v>22</v>
       </c>
       <c r="D164" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E164" t="s">
+        <v>543</v>
+      </c>
+      <c r="F164" t="s">
         <v>542</v>
       </c>
-      <c r="F164" t="s">
-        <v>541</v>
-      </c>
       <c r="H164">
         <v>0</v>
       </c>
@@ -12495,22 +12844,25 @@
         <v>28</v>
       </c>
       <c r="N164" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O164" t="s">
         <v>30</v>
       </c>
       <c r="Q164" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="R164" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="S164" t="s">
         <v>31</v>
       </c>
       <c r="T164" t="s">
-        <v>522</v>
+        <v>523</v>
+      </c>
+      <c r="U164" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.3">
@@ -12521,14 +12873,14 @@
         <v>22</v>
       </c>
       <c r="D165" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E165" t="s">
+        <v>546</v>
+      </c>
+      <c r="F165" t="s">
         <v>545</v>
       </c>
-      <c r="F165" t="s">
-        <v>544</v>
-      </c>
       <c r="H165">
         <v>0</v>
       </c>
@@ -12545,22 +12897,22 @@
         <v>28</v>
       </c>
       <c r="N165" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O165" t="s">
         <v>30</v>
       </c>
       <c r="Q165" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="R165" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="S165" t="s">
         <v>31</v>
       </c>
       <c r="T165" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="U165" t="s">
         <v>72</v>
@@ -12574,14 +12926,14 @@
         <v>22</v>
       </c>
       <c r="D166" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E166" t="s">
+        <v>549</v>
+      </c>
+      <c r="F166" t="s">
         <v>548</v>
       </c>
-      <c r="F166" t="s">
-        <v>547</v>
-      </c>
       <c r="H166">
         <v>0</v>
       </c>
@@ -12598,22 +12950,25 @@
         <v>28</v>
       </c>
       <c r="N166" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O166" t="s">
         <v>30</v>
       </c>
       <c r="Q166" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="R166" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="S166" t="s">
         <v>31</v>
       </c>
       <c r="T166" t="s">
-        <v>550</v>
+        <v>551</v>
+      </c>
+      <c r="U166" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -12624,46 +12979,49 @@
         <v>22</v>
       </c>
       <c r="D167" t="s">
+        <v>552</v>
+      </c>
+      <c r="E167" t="s">
+        <v>553</v>
+      </c>
+      <c r="F167" t="s">
+        <v>552</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167" t="s">
+        <v>25</v>
+      </c>
+      <c r="J167" t="s">
+        <v>26</v>
+      </c>
+      <c r="K167" t="s">
+        <v>27</v>
+      </c>
+      <c r="M167" t="s">
+        <v>28</v>
+      </c>
+      <c r="N167" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="O167" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>552</v>
+      </c>
+      <c r="R167" t="s">
+        <v>552</v>
+      </c>
+      <c r="S167" t="s">
+        <v>31</v>
+      </c>
+      <c r="T167" t="s">
         <v>551</v>
       </c>
-      <c r="E167" t="s">
-        <v>552</v>
-      </c>
-      <c r="F167" t="s">
-        <v>551</v>
-      </c>
-      <c r="H167">
-        <v>0</v>
-      </c>
-      <c r="I167" t="s">
-        <v>25</v>
-      </c>
-      <c r="J167" t="s">
-        <v>26</v>
-      </c>
-      <c r="K167" t="s">
-        <v>27</v>
-      </c>
-      <c r="M167" t="s">
-        <v>28</v>
-      </c>
-      <c r="N167" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="O167" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q167" t="s">
-        <v>551</v>
-      </c>
-      <c r="R167" t="s">
-        <v>551</v>
-      </c>
-      <c r="S167" t="s">
-        <v>31</v>
-      </c>
-      <c r="T167" t="s">
-        <v>550</v>
+      <c r="U167" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.3">
@@ -12674,14 +13032,14 @@
         <v>22</v>
       </c>
       <c r="D168" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E168" t="s">
+        <v>556</v>
+      </c>
+      <c r="F168" t="s">
         <v>555</v>
       </c>
-      <c r="F168" t="s">
-        <v>554</v>
-      </c>
       <c r="H168">
         <v>0</v>
       </c>
@@ -12698,22 +13056,22 @@
         <v>28</v>
       </c>
       <c r="N168" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O168" t="s">
         <v>30</v>
       </c>
       <c r="Q168" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="R168" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S168" t="s">
         <v>31</v>
       </c>
       <c r="T168" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="U168" t="s">
         <v>72</v>
@@ -12727,14 +13085,14 @@
         <v>22</v>
       </c>
       <c r="D169" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E169" t="s">
+        <v>559</v>
+      </c>
+      <c r="F169" t="s">
         <v>558</v>
       </c>
-      <c r="F169" t="s">
-        <v>557</v>
-      </c>
       <c r="H169">
         <v>0</v>
       </c>
@@ -12751,22 +13109,25 @@
         <v>28</v>
       </c>
       <c r="N169" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O169" t="s">
         <v>30</v>
       </c>
       <c r="Q169" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="R169" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="S169" t="s">
         <v>31</v>
       </c>
       <c r="T169" t="s">
-        <v>550</v>
+        <v>551</v>
+      </c>
+      <c r="U169" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="170" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -12777,14 +13138,14 @@
         <v>22</v>
       </c>
       <c r="D170" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E170" t="s">
+        <v>562</v>
+      </c>
+      <c r="F170" t="s">
         <v>561</v>
       </c>
-      <c r="F170" t="s">
-        <v>560</v>
-      </c>
       <c r="H170">
         <v>0</v>
       </c>
@@ -12801,22 +13162,25 @@
         <v>28</v>
       </c>
       <c r="N170" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O170" t="s">
         <v>30</v>
       </c>
       <c r="Q170" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="R170" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="S170" t="s">
         <v>31</v>
       </c>
       <c r="T170" t="s">
-        <v>550</v>
+        <v>551</v>
+      </c>
+      <c r="U170" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.3">
@@ -12827,14 +13191,14 @@
         <v>22</v>
       </c>
       <c r="D171" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E171" t="s">
+        <v>565</v>
+      </c>
+      <c r="F171" t="s">
         <v>564</v>
       </c>
-      <c r="F171" t="s">
-        <v>563</v>
-      </c>
       <c r="H171">
         <v>0</v>
       </c>
@@ -12851,22 +13215,22 @@
         <v>28</v>
       </c>
       <c r="N171" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O171" t="s">
         <v>30</v>
       </c>
       <c r="Q171" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="R171" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="S171" t="s">
         <v>31</v>
       </c>
       <c r="T171" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="U171" t="s">
         <v>72</v>
@@ -12880,14 +13244,14 @@
         <v>22</v>
       </c>
       <c r="D172" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E172" t="s">
+        <v>568</v>
+      </c>
+      <c r="F172" t="s">
         <v>567</v>
       </c>
-      <c r="F172" t="s">
-        <v>566</v>
-      </c>
       <c r="H172">
         <v>0</v>
       </c>
@@ -12904,22 +13268,25 @@
         <v>28</v>
       </c>
       <c r="N172" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O172" t="s">
         <v>30</v>
       </c>
       <c r="Q172" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="R172" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="S172" t="s">
         <v>31</v>
       </c>
       <c r="T172" t="s">
-        <v>550</v>
+        <v>551</v>
+      </c>
+      <c r="U172" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="173" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -12930,14 +13297,14 @@
         <v>22</v>
       </c>
       <c r="D173" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E173" t="s">
+        <v>571</v>
+      </c>
+      <c r="F173" t="s">
         <v>570</v>
       </c>
-      <c r="F173" t="s">
-        <v>569</v>
-      </c>
       <c r="H173">
         <v>0</v>
       </c>
@@ -12954,22 +13321,25 @@
         <v>28</v>
       </c>
       <c r="N173" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O173" t="s">
         <v>30</v>
       </c>
       <c r="Q173" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="R173" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="S173" t="s">
         <v>31</v>
       </c>
       <c r="T173" t="s">
-        <v>550</v>
+        <v>551</v>
+      </c>
+      <c r="U173" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.3">
@@ -12980,14 +13350,14 @@
         <v>22</v>
       </c>
       <c r="D174" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E174" t="s">
+        <v>574</v>
+      </c>
+      <c r="F174" t="s">
         <v>573</v>
       </c>
-      <c r="F174" t="s">
-        <v>572</v>
-      </c>
       <c r="H174">
         <v>0</v>
       </c>
@@ -13004,22 +13374,22 @@
         <v>28</v>
       </c>
       <c r="N174" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O174" t="s">
         <v>30</v>
       </c>
       <c r="Q174" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="R174" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="S174" t="s">
         <v>31</v>
       </c>
       <c r="T174" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="U174" t="s">
         <v>72</v>
@@ -13033,14 +13403,14 @@
         <v>22</v>
       </c>
       <c r="D175" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E175" t="s">
+        <v>577</v>
+      </c>
+      <c r="F175" t="s">
         <v>576</v>
       </c>
-      <c r="F175" t="s">
-        <v>575</v>
-      </c>
       <c r="H175">
         <v>0</v>
       </c>
@@ -13057,22 +13427,25 @@
         <v>28</v>
       </c>
       <c r="N175" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O175" t="s">
         <v>30</v>
       </c>
       <c r="Q175" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="R175" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="S175" t="s">
         <v>31</v>
       </c>
       <c r="T175" t="s">
-        <v>578</v>
+        <v>579</v>
+      </c>
+      <c r="U175" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="176" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
@@ -13083,46 +13456,49 @@
         <v>22</v>
       </c>
       <c r="D176" t="s">
+        <v>580</v>
+      </c>
+      <c r="E176" t="s">
+        <v>581</v>
+      </c>
+      <c r="F176" t="s">
+        <v>580</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+      <c r="I176" t="s">
+        <v>25</v>
+      </c>
+      <c r="J176" t="s">
+        <v>26</v>
+      </c>
+      <c r="K176" t="s">
+        <v>27</v>
+      </c>
+      <c r="M176" t="s">
+        <v>28</v>
+      </c>
+      <c r="N176" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="O176" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>580</v>
+      </c>
+      <c r="R176" t="s">
+        <v>580</v>
+      </c>
+      <c r="S176" t="s">
+        <v>31</v>
+      </c>
+      <c r="T176" t="s">
         <v>579</v>
       </c>
-      <c r="E176" t="s">
-        <v>580</v>
-      </c>
-      <c r="F176" t="s">
-        <v>579</v>
-      </c>
-      <c r="H176">
-        <v>0</v>
-      </c>
-      <c r="I176" t="s">
-        <v>25</v>
-      </c>
-      <c r="J176" t="s">
-        <v>26</v>
-      </c>
-      <c r="K176" t="s">
-        <v>27</v>
-      </c>
-      <c r="M176" t="s">
-        <v>28</v>
-      </c>
-      <c r="N176" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="O176" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q176" t="s">
-        <v>579</v>
-      </c>
-      <c r="R176" t="s">
-        <v>579</v>
-      </c>
-      <c r="S176" t="s">
-        <v>31</v>
-      </c>
-      <c r="T176" t="s">
-        <v>578</v>
+      <c r="U176" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="177" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -13133,14 +13509,14 @@
         <v>22</v>
       </c>
       <c r="D177" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E177" t="s">
+        <v>584</v>
+      </c>
+      <c r="F177" t="s">
         <v>583</v>
       </c>
-      <c r="F177" t="s">
-        <v>582</v>
-      </c>
       <c r="H177">
         <v>0</v>
       </c>
@@ -13157,22 +13533,25 @@
         <v>28</v>
       </c>
       <c r="N177" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O177" t="s">
         <v>30</v>
       </c>
       <c r="Q177" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="R177" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="S177" t="s">
         <v>31</v>
       </c>
       <c r="T177" t="s">
-        <v>578</v>
+        <v>579</v>
+      </c>
+      <c r="U177" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.3">
@@ -13183,14 +13562,14 @@
         <v>22</v>
       </c>
       <c r="D178" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E178" t="s">
+        <v>587</v>
+      </c>
+      <c r="F178" t="s">
         <v>586</v>
       </c>
-      <c r="F178" t="s">
-        <v>585</v>
-      </c>
       <c r="H178">
         <v>0</v>
       </c>
@@ -13207,22 +13586,22 @@
         <v>28</v>
       </c>
       <c r="N178" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O178" t="s">
         <v>30</v>
       </c>
       <c r="Q178" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="R178" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="S178" t="s">
         <v>31</v>
       </c>
       <c r="T178" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="U178" t="s">
         <v>72</v>
@@ -13236,14 +13615,14 @@
         <v>22</v>
       </c>
       <c r="D179" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E179" t="s">
+        <v>590</v>
+      </c>
+      <c r="F179" t="s">
         <v>589</v>
       </c>
-      <c r="F179" t="s">
-        <v>588</v>
-      </c>
       <c r="H179">
         <v>0</v>
       </c>
@@ -13260,16 +13639,16 @@
         <v>28</v>
       </c>
       <c r="N179" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O179" t="s">
         <v>30</v>
       </c>
       <c r="Q179" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="R179" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="S179" t="s">
         <v>31</v>
@@ -13286,14 +13665,14 @@
         <v>22</v>
       </c>
       <c r="D180" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E180" t="s">
+        <v>593</v>
+      </c>
+      <c r="F180" t="s">
         <v>592</v>
       </c>
-      <c r="F180" t="s">
-        <v>591</v>
-      </c>
       <c r="H180">
         <v>0</v>
       </c>
@@ -13310,16 +13689,16 @@
         <v>28</v>
       </c>
       <c r="N180" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O180" t="s">
         <v>30</v>
       </c>
       <c r="Q180" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="R180" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="S180" t="s">
         <v>31</v>
@@ -13328,7 +13707,7 @@
         <v>48</v>
       </c>
       <c r="U180" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.3">
@@ -13339,14 +13718,14 @@
         <v>22</v>
       </c>
       <c r="D181" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E181" t="s">
+        <v>597</v>
+      </c>
+      <c r="F181" t="s">
         <v>596</v>
       </c>
-      <c r="F181" t="s">
-        <v>595</v>
-      </c>
       <c r="H181">
         <v>0</v>
       </c>
@@ -13363,16 +13742,16 @@
         <v>28</v>
       </c>
       <c r="N181" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O181" t="s">
         <v>30</v>
       </c>
       <c r="Q181" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="R181" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="S181" t="s">
         <v>31</v>
@@ -13389,14 +13768,14 @@
         <v>22</v>
       </c>
       <c r="D182" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E182" t="s">
+        <v>600</v>
+      </c>
+      <c r="F182" t="s">
         <v>599</v>
       </c>
-      <c r="F182" t="s">
-        <v>598</v>
-      </c>
       <c r="H182">
         <v>0</v>
       </c>
@@ -13413,16 +13792,16 @@
         <v>28</v>
       </c>
       <c r="N182" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O182" t="s">
         <v>30</v>
       </c>
       <c r="Q182" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="R182" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="S182" t="s">
         <v>31</v>
@@ -13439,14 +13818,14 @@
         <v>22</v>
       </c>
       <c r="D183" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E183" t="s">
+        <v>603</v>
+      </c>
+      <c r="F183" t="s">
         <v>602</v>
       </c>
-      <c r="F183" t="s">
-        <v>601</v>
-      </c>
       <c r="H183">
         <v>0</v>
       </c>
@@ -13463,16 +13842,16 @@
         <v>28</v>
       </c>
       <c r="N183" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O183" t="s">
         <v>30</v>
       </c>
       <c r="Q183" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="R183" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="S183" t="s">
         <v>31</v>
@@ -13489,14 +13868,14 @@
         <v>22</v>
       </c>
       <c r="D184" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E184" t="s">
+        <v>606</v>
+      </c>
+      <c r="F184" t="s">
         <v>605</v>
       </c>
-      <c r="F184" t="s">
-        <v>604</v>
-      </c>
       <c r="H184">
         <v>0</v>
       </c>
@@ -13513,16 +13892,16 @@
         <v>28</v>
       </c>
       <c r="N184" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O184" t="s">
         <v>30</v>
       </c>
       <c r="Q184" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R184" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="S184" t="s">
         <v>31</v>
@@ -13531,7 +13910,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:21" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>21</v>
       </c>
@@ -13539,14 +13918,14 @@
         <v>22</v>
       </c>
       <c r="D185" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E185" t="s">
+        <v>609</v>
+      </c>
+      <c r="F185" t="s">
         <v>608</v>
       </c>
-      <c r="F185" t="s">
-        <v>607</v>
-      </c>
       <c r="H185">
         <v>0</v>
       </c>
@@ -13562,17 +13941,17 @@
       <c r="M185" t="s">
         <v>28</v>
       </c>
-      <c r="N185" t="s">
-        <v>609</v>
+      <c r="N185" s="2" t="s">
+        <v>610</v>
       </c>
       <c r="O185" t="s">
         <v>30</v>
       </c>
       <c r="Q185" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="R185" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="S185" t="s">
         <v>31</v>
@@ -13580,11 +13959,8 @@
       <c r="T185" t="s">
         <v>48</v>
       </c>
-      <c r="U185" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="186" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>21</v>
       </c>
@@ -13615,7 +13991,7 @@
       <c r="M186" t="s">
         <v>28</v>
       </c>
-      <c r="N186" s="2" t="s">
+      <c r="N186" t="s">
         <v>613</v>
       </c>
       <c r="O186" t="s">
@@ -13631,10 +14007,13 @@
         <v>31</v>
       </c>
       <c r="T186" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="187" spans="1:21" ht="144" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="U186" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="187" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>21</v>
       </c>
@@ -13665,7 +14044,7 @@
       <c r="M187" t="s">
         <v>28</v>
       </c>
-      <c r="N187" s="2" t="s">
+      <c r="N187" t="s">
         <v>616</v>
       </c>
       <c r="O187" t="s">
@@ -13681,7 +14060,7 @@
         <v>31</v>
       </c>
       <c r="T187" t="s">
-        <v>48</v>
+        <v>617</v>
       </c>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.3">
@@ -13692,99 +14071,96 @@
         <v>22</v>
       </c>
       <c r="D188" t="s">
+        <v>618</v>
+      </c>
+      <c r="E188" t="s">
+        <v>619</v>
+      </c>
+      <c r="F188" t="s">
+        <v>618</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188" t="s">
+        <v>25</v>
+      </c>
+      <c r="J188" t="s">
+        <v>26</v>
+      </c>
+      <c r="K188" t="s">
+        <v>27</v>
+      </c>
+      <c r="M188" t="s">
+        <v>28</v>
+      </c>
+      <c r="N188" t="s">
+        <v>620</v>
+      </c>
+      <c r="O188" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>618</v>
+      </c>
+      <c r="R188" t="s">
+        <v>618</v>
+      </c>
+      <c r="S188" t="s">
+        <v>31</v>
+      </c>
+      <c r="T188" t="s">
         <v>617</v>
       </c>
-      <c r="E188" t="s">
-        <v>618</v>
-      </c>
-      <c r="F188" t="s">
+    </row>
+    <row r="189" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>21</v>
+      </c>
+      <c r="C189" t="s">
+        <v>22</v>
+      </c>
+      <c r="D189" t="s">
+        <v>621</v>
+      </c>
+      <c r="E189" t="s">
+        <v>622</v>
+      </c>
+      <c r="F189" t="s">
+        <v>621</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189" t="s">
+        <v>25</v>
+      </c>
+      <c r="J189" t="s">
+        <v>26</v>
+      </c>
+      <c r="K189" t="s">
+        <v>27</v>
+      </c>
+      <c r="M189" t="s">
+        <v>28</v>
+      </c>
+      <c r="N189" t="s">
+        <v>623</v>
+      </c>
+      <c r="O189" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>621</v>
+      </c>
+      <c r="R189" t="s">
+        <v>621</v>
+      </c>
+      <c r="S189" t="s">
+        <v>31</v>
+      </c>
+      <c r="T189" t="s">
         <v>617</v>
-      </c>
-      <c r="H188">
-        <v>0</v>
-      </c>
-      <c r="I188" t="s">
-        <v>25</v>
-      </c>
-      <c r="J188" t="s">
-        <v>26</v>
-      </c>
-      <c r="K188" t="s">
-        <v>27</v>
-      </c>
-      <c r="M188" t="s">
-        <v>28</v>
-      </c>
-      <c r="N188" t="s">
-        <v>619</v>
-      </c>
-      <c r="O188" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q188" t="s">
-        <v>617</v>
-      </c>
-      <c r="R188" t="s">
-        <v>617</v>
-      </c>
-      <c r="S188" t="s">
-        <v>31</v>
-      </c>
-      <c r="T188" t="s">
-        <v>48</v>
-      </c>
-      <c r="U188" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="189" spans="1:21" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
-        <v>21</v>
-      </c>
-      <c r="C189" t="s">
-        <v>22</v>
-      </c>
-      <c r="D189" t="s">
-        <v>620</v>
-      </c>
-      <c r="E189" t="s">
-        <v>621</v>
-      </c>
-      <c r="F189" t="s">
-        <v>620</v>
-      </c>
-      <c r="H189">
-        <v>0</v>
-      </c>
-      <c r="I189" t="s">
-        <v>25</v>
-      </c>
-      <c r="J189" t="s">
-        <v>26</v>
-      </c>
-      <c r="K189" t="s">
-        <v>27</v>
-      </c>
-      <c r="M189" t="s">
-        <v>28</v>
-      </c>
-      <c r="N189" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="O189" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q189" t="s">
-        <v>620</v>
-      </c>
-      <c r="R189" t="s">
-        <v>620</v>
-      </c>
-      <c r="S189" t="s">
-        <v>31</v>
-      </c>
-      <c r="T189" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.3">
@@ -13795,14 +14171,14 @@
         <v>22</v>
       </c>
       <c r="D190" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E190" t="s">
+        <v>625</v>
+      </c>
+      <c r="F190" t="s">
         <v>624</v>
       </c>
-      <c r="F190" t="s">
-        <v>623</v>
-      </c>
       <c r="H190">
         <v>0</v>
       </c>
@@ -13819,25 +14195,22 @@
         <v>28</v>
       </c>
       <c r="N190" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O190" t="s">
         <v>30</v>
       </c>
       <c r="Q190" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="R190" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="S190" t="s">
         <v>31</v>
       </c>
       <c r="T190" t="s">
-        <v>31</v>
-      </c>
-      <c r="U190" t="s">
-        <v>32</v>
+        <v>617</v>
       </c>
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.3">
@@ -13848,14 +14221,14 @@
         <v>22</v>
       </c>
       <c r="D191" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E191" t="s">
+        <v>628</v>
+      </c>
+      <c r="F191" t="s">
         <v>627</v>
       </c>
-      <c r="F191" t="s">
-        <v>626</v>
-      </c>
       <c r="H191">
         <v>0</v>
       </c>
@@ -13872,25 +14245,25 @@
         <v>28</v>
       </c>
       <c r="N191" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O191" t="s">
         <v>30</v>
       </c>
       <c r="Q191" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="R191" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="S191" t="s">
         <v>31</v>
       </c>
       <c r="T191" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="192" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>21</v>
       </c>
@@ -13921,7 +14294,7 @@
       <c r="M192" t="s">
         <v>28</v>
       </c>
-      <c r="N192" t="s">
+      <c r="N192" s="2" t="s">
         <v>632</v>
       </c>
       <c r="O192" t="s">
@@ -13937,10 +14310,10 @@
         <v>31</v>
       </c>
       <c r="T192" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="193" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>21</v>
       </c>
@@ -13971,7 +14344,7 @@
       <c r="M193" t="s">
         <v>28</v>
       </c>
-      <c r="N193" t="s">
+      <c r="N193" s="2" t="s">
         <v>635</v>
       </c>
       <c r="O193" t="s">
@@ -13987,10 +14360,10 @@
         <v>31</v>
       </c>
       <c r="T193" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="194" spans="1:21" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>21</v>
       </c>
@@ -14021,7 +14394,7 @@
       <c r="M194" t="s">
         <v>28</v>
       </c>
-      <c r="N194" t="s">
+      <c r="N194" s="2" t="s">
         <v>638</v>
       </c>
       <c r="O194" t="s">
@@ -14037,10 +14410,10 @@
         <v>31</v>
       </c>
       <c r="T194" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="195" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>21</v>
       </c>
@@ -14071,7 +14444,7 @@
       <c r="M195" t="s">
         <v>28</v>
       </c>
-      <c r="N195" t="s">
+      <c r="N195" s="2" t="s">
         <v>641</v>
       </c>
       <c r="O195" t="s">
@@ -14087,10 +14460,10 @@
         <v>31</v>
       </c>
       <c r="T195" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="196" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="196" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>21</v>
       </c>
@@ -14137,10 +14510,10 @@
         <v>31</v>
       </c>
       <c r="T196" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="197" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="197" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>21</v>
       </c>
@@ -14171,7 +14544,7 @@
       <c r="M197" t="s">
         <v>28</v>
       </c>
-      <c r="N197" s="2" t="s">
+      <c r="N197" t="s">
         <v>647</v>
       </c>
       <c r="O197" t="s">
@@ -14187,10 +14560,10 @@
         <v>31</v>
       </c>
       <c r="T197" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="198" spans="1:20" ht="172.8" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="198" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>21</v>
       </c>
@@ -14221,7 +14594,7 @@
       <c r="M198" t="s">
         <v>28</v>
       </c>
-      <c r="N198" s="2" t="s">
+      <c r="N198" t="s">
         <v>650</v>
       </c>
       <c r="O198" t="s">
@@ -14237,10 +14610,10 @@
         <v>31</v>
       </c>
       <c r="T198" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="199" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="199" spans="1:21" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>21</v>
       </c>
@@ -14287,10 +14660,10 @@
         <v>31</v>
       </c>
       <c r="T199" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="200" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="200" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>21</v>
       </c>
@@ -14321,7 +14694,7 @@
       <c r="M200" t="s">
         <v>28</v>
       </c>
-      <c r="N200" s="2" t="s">
+      <c r="N200" t="s">
         <v>656</v>
       </c>
       <c r="O200" t="s">
@@ -14337,10 +14710,10 @@
         <v>31</v>
       </c>
       <c r="T200" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="201" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>21</v>
       </c>
@@ -14387,10 +14760,10 @@
         <v>31</v>
       </c>
       <c r="T201" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="202" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>21</v>
       </c>
@@ -14421,7 +14794,7 @@
       <c r="M202" t="s">
         <v>28</v>
       </c>
-      <c r="N202" t="s">
+      <c r="N202" s="2" t="s">
         <v>662</v>
       </c>
       <c r="O202" t="s">
@@ -14437,10 +14810,13 @@
         <v>31</v>
       </c>
       <c r="T202" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="203" spans="1:20" ht="115.2" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="U202" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="203" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>21</v>
       </c>
@@ -14475,7 +14851,7 @@
         <v>665</v>
       </c>
       <c r="O203" t="s">
-        <v>30</v>
+        <v>666</v>
       </c>
       <c r="Q203" t="s">
         <v>663</v>
@@ -14484,13 +14860,13 @@
         <v>663</v>
       </c>
       <c r="S203" t="s">
-        <v>31</v>
+        <v>667</v>
       </c>
       <c r="T203" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.3">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="204" spans="1:21" ht="144" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>21</v>
       </c>
@@ -14498,13 +14874,13 @@
         <v>22</v>
       </c>
       <c r="D204" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E204" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="F204" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="H204">
         <v>0</v>
@@ -14521,26 +14897,26 @@
       <c r="M204" t="s">
         <v>28</v>
       </c>
-      <c r="N204" t="s">
-        <v>668</v>
+      <c r="N204" s="2" t="s">
+        <v>671</v>
       </c>
       <c r="O204" t="s">
         <v>30</v>
       </c>
       <c r="Q204" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="R204" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="S204" t="s">
-        <v>31</v>
+        <v>672</v>
       </c>
       <c r="T204" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="205" spans="1:21" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>21</v>
       </c>
@@ -14548,13 +14924,13 @@
         <v>22</v>
       </c>
       <c r="D205" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E205" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F205" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="H205">
         <v>0</v>
@@ -14571,26 +14947,26 @@
       <c r="M205" t="s">
         <v>28</v>
       </c>
-      <c r="N205" t="s">
-        <v>671</v>
+      <c r="N205" s="2" t="s">
+        <v>675</v>
       </c>
       <c r="O205" t="s">
         <v>30</v>
       </c>
       <c r="Q205" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="R205" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="S205" t="s">
-        <v>31</v>
+        <v>676</v>
       </c>
       <c r="T205" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="206" spans="1:20" ht="144" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="206" spans="1:21" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>21</v>
       </c>
@@ -14598,13 +14974,13 @@
         <v>22</v>
       </c>
       <c r="D206" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="E206" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="F206" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="H206">
         <v>0</v>
@@ -14622,25 +14998,25 @@
         <v>28</v>
       </c>
       <c r="N206" s="2" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="O206" t="s">
-        <v>675</v>
+        <v>30</v>
       </c>
       <c r="Q206" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="R206" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="S206" t="s">
         <v>676</v>
       </c>
       <c r="T206" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="207" spans="1:20" ht="144" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="207" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>21</v>
       </c>
@@ -14648,16 +15024,16 @@
         <v>22</v>
       </c>
       <c r="D207" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E207" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="F207" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H207">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="I207" t="s">
         <v>25</v>
@@ -14671,74 +15047,24 @@
       <c r="M207" t="s">
         <v>28</v>
       </c>
-      <c r="N207" s="2" t="s">
+      <c r="N207" t="s">
+        <v>682</v>
+      </c>
+      <c r="O207" t="s">
+        <v>666</v>
+      </c>
+      <c r="Q207" t="s">
         <v>680</v>
       </c>
-      <c r="O207" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q207" t="s">
-        <v>678</v>
-      </c>
       <c r="R207" t="s">
-        <v>678</v>
-      </c>
-      <c r="S207" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="T207" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>21</v>
-      </c>
-      <c r="C208" t="s">
-        <v>22</v>
-      </c>
-      <c r="D208" t="s">
-        <v>682</v>
-      </c>
-      <c r="E208" t="s">
-        <v>683</v>
-      </c>
-      <c r="F208" t="s">
-        <v>682</v>
-      </c>
-      <c r="H208">
-        <v>127</v>
-      </c>
-      <c r="I208" t="s">
-        <v>25</v>
-      </c>
-      <c r="J208" t="s">
-        <v>26</v>
-      </c>
-      <c r="K208" t="s">
-        <v>27</v>
-      </c>
-      <c r="M208" t="s">
-        <v>28</v>
-      </c>
-      <c r="N208" t="s">
-        <v>684</v>
-      </c>
-      <c r="O208" t="s">
-        <v>675</v>
-      </c>
-      <c r="Q208" t="s">
-        <v>682</v>
-      </c>
-      <c r="R208" t="s">
-        <v>682</v>
-      </c>
-      <c r="T208" t="s">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:U208" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U207" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data source/MDSCHEMA_MEASURES.xlsx
+++ b/Data source/MDSCHEMA_MEASURES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ksoszka-my.sharepoint.com/personal/kamil_soszka_ksoszka_onmicrosoft_com/Documents/Kamil Soszka Business Intelligence/Data source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_0A58AA8DC5968491FEE2F8C6E90ADB510A9F2A16" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{646867E9-910E-483B-A074-5FD4B1B3DA62}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_0A58AA8DC5968491FEE2F85B91532B220499CBC8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF8E8D93-890A-486C-A23E-32C62CE610F0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Query1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Query1!$A$1:$U$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Query1!$A$1:$U$227</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3604" uniqueCount="745">
   <si>
     <t>CATALOG_NAME</t>
   </si>
@@ -88,7 +88,7 @@
     <t>DEFAULT_FORMAT_STRING</t>
   </si>
   <si>
-    <t>b8ff92da-95d5-43b5-ab54-707ffae4b929</t>
+    <t>796dc774-098d-4d6e-8e39-55b07ef33e8e</t>
   </si>
   <si>
     <t>Model</t>
@@ -121,7 +121,7 @@
     <t>Model_Measures</t>
   </si>
   <si>
-    <t>#,##0;(#,##0)</t>
+    <t>#,,#</t>
   </si>
   <si>
     <t>__profit</t>
@@ -2057,9 +2057,6 @@
   </si>
   <si>
     <t>Time intelligence\Moving annual growth\__sales</t>
-  </si>
-  <si>
-    <t>$ #,##0</t>
   </si>
   <si>
     <t>PYMAT __sales</t>
@@ -3649,6 +3646,403 @@
     Result</t>
   </si>
   <si>
+    <t>TI_PL (profit)</t>
+  </si>
+  <si>
+    <t>[Measures].[TI_PL (profit)]</t>
+  </si>
+  <si>
+    <t>VAR Result =
+    [__profit]
+        + ( RAND () * [__profit] )
+        - ( RAND () * [__profit] )
+RETURN
+    ABS ( Result )</t>
+  </si>
+  <si>
+    <t>Time intelligence\KPI</t>
+  </si>
+  <si>
+    <t>TI_PL %</t>
+  </si>
+  <si>
+    <t>[Measures].[TI_PL %]</t>
+  </si>
+  <si>
+    <t>DIVIDE (
+    ABS ( [__profit] + ( RAND () * [__profit] ) - ( RAND () * [__profit] ) ),
+    [__profit]
+)</t>
+  </si>
+  <si>
+    <t>0%;-0%;0%</t>
+  </si>
+  <si>
+    <t>TI_KPI</t>
+  </si>
+  <si>
+    <t>[Measures].[TI_KPI]</t>
+  </si>
+  <si>
+    <t>VAR Result =
+    SWITCH (
+        TRUE (),
+        DIVIDE (
+            ABS ( [__profit] + ( RAND () * [__profit] ) - ( RAND () * [__profit] ) ),
+            [__profit]
+        ) &gt; 0, "🔼",
+        DIVIDE (
+            ABS ( [__profit] + ( RAND () * [__profit] ) - ( RAND () * [__profit] ) ),
+            [__profit]
+        ) &lt; 0, "🔽",
+        BLANK ()
+    )
+RETURN
+    SWITCH ( TRUE (), HASONEVALUE ( 'Date'[Month] ), Result )</t>
+  </si>
+  <si>
+    <t>OFFSET-1</t>
+  </si>
+  <si>
+    <t>[Measures].[OFFSET-1]</t>
+  </si>
+  <si>
+    <t>VAR _1D =
+    CALCULATE (
+        [__profit],
+        OFFSET ( -1, ALL ( 'Date'[Date] ), ORDERBY ( 'Date'[Date], ASC ) )
+    )
+VAR _1M =
+    CALCULATE (
+        [__profit],
+        OFFSET (
+            -1,
+            ALL ( 'Date'[Year Month Number], 'Date'[Year Month] ),
+            ORDERBY ( 'Date'[Year Month Number], ASC )
+        )
+    )
+VAR _1Y =
+    CALCULATE (
+        [__profit],
+        OFFSET ( -1, ALL ( 'Date'[Year] ), ORDERBY ( 'Date'[Year], ASC ) )
+    )
+VAR Result =
+    SWITCH (
+        TRUE,
+        ISINSCOPE ( 'Date'[Date] ), _1D,
+        ISINSCOPE ( 'Date'[Year Month] ), _1M,
+        ISINSCOPE ( 'Date'[Year] ), _1Y
+    )
+RETURN
+    Result</t>
+  </si>
+  <si>
+    <t>New DAX Functions</t>
+  </si>
+  <si>
+    <t>WINDOW -1</t>
+  </si>
+  <si>
+    <t>[Measures].[WINDOW -1]</t>
+  </si>
+  <si>
+    <t>VAR _1D =
+    CALCULATE (
+        [__profit],
+        WINDOW (
+            1,
+            REL,
+            1,
+            REL,
+            SUMMARIZE ( ALLSELECTED ( 'Date' ), 'Date'[Date] ),
+            ORDERBY ( 'Date'[Date], DESC )
+        )
+    )
+VAR _1M =
+    CALCULATE (
+        [__profit],
+        WINDOW (
+            1,
+            REL,
+            1,
+            REL,
+            SUMMARIZE (
+                ALLSELECTED ( 'Date' ),
+                'Date'[Year Month Number],
+                'Date'[Year Month]
+            ),
+            ORDERBY ( 'Date'[Year Month Number], DESC )
+        )
+    )
+VAR _1Y =
+    CALCULATE (
+        [__profit],
+        WINDOW (
+            1,
+            REL,
+            1,
+            REL,
+            SUMMARIZE ( ALLSELECTED ( 'Date' ), 'Date'[Year] ),
+            ORDERBY ( 'Date'[Year], DESC )
+        )
+    )
+VAR Result =
+    SWITCH (
+        TRUE,
+        ISINSCOPE ( 'Date'[Date] ), _1D,
+        ISINSCOPE ( 'Date'[Year Month] ), _1M,
+        ISINSCOPE ( 'Date'[Year] ), _1Y
+    )
+RETURN
+    Result</t>
+  </si>
+  <si>
+    <t>OFFSET-0</t>
+  </si>
+  <si>
+    <t>[Measures].[OFFSET-0]</t>
+  </si>
+  <si>
+    <t>VAR _0D =
+    CALCULATE (
+        [__profit],
+        OFFSET ( -0, ALL ( 'Date'[Date] ), ORDERBY ( 'Date'[Date], ASC ) )
+    )
+VAR _0M =
+    CALCULATE (
+        [__profit],
+        OFFSET (
+            -0,
+            ALL ( 'Date'[Year Month Number], 'Date'[Year Month] ),
+            ORDERBY ( 'Date'[Year Month Number], ASC )
+        )
+    )
+VAR _0Y =
+    CALCULATE (
+        [__profit],
+        OFFSET ( -0, ALL ( 'Date'[Year] ), ORDERBY ( 'Date'[Year], ASC ) )
+    )
+VAR Result =
+    SWITCH (
+        TRUE,
+        ISINSCOPE ( 'Date'[Date] ), _0D,
+        ISINSCOPE ( 'Date'[Year Month] ), _0M,
+        ISINSCOPE ( 'Date'[Year] ), _0Y
+    )
+RETURN
+    Result</t>
+  </si>
+  <si>
+    <t>WINDOW -0</t>
+  </si>
+  <si>
+    <t>[Measures].[WINDOW -0]</t>
+  </si>
+  <si>
+    <t>VAR _0D =
+    CALCULATE (
+        [__profit],
+        WINDOW (
+            0,
+            REL,
+            0,
+            REL,
+            SUMMARIZE ( ALLSELECTED ( 'Date' ), 'Date'[Date] ),
+            ORDERBY ( 'Date'[Date], DESC )
+        )
+    )
+VAR _0M =
+    CALCULATE (
+        [__profit],
+        WINDOW (
+            0,
+            REL,
+            0,
+            REL,
+            SUMMARIZE (
+                ALLSELECTED ( 'Date' ),
+                'Date'[Year Month Number],
+                'Date'[Year Month]
+            ),
+            ORDERBY ( 'Date'[Year Month Number], DESC )
+        )
+    )
+VAR _0Y =
+    CALCULATE (
+        [__profit],
+        WINDOW (
+            0,
+            REL,
+            0,
+            REL,
+            SUMMARIZE ( ALLSELECTED ( 'Date' ), 'Date'[Year] ),
+            ORDERBY ( 'Date'[Year], DESC )
+        )
+    )
+VAR Result =
+    SWITCH (
+        TRUE,
+        ISINSCOPE ( 'Date'[Date] ), _0D,
+        ISINSCOPE ( 'Date'[Year Month] ), _0M,
+        ISINSCOPE ( 'Date'[Year] ), _0Y
+    )
+RETURN
+    Result</t>
+  </si>
+  <si>
+    <t>OFFSET DELTA</t>
+  </si>
+  <si>
+    <t>[Measures].[OFFSET DELTA]</t>
+  </si>
+  <si>
+    <t>[OFFSET-0] - [OFFSET-1]</t>
+  </si>
+  <si>
+    <t>OFFSET EVO</t>
+  </si>
+  <si>
+    <t>[Measures].[OFFSET EVO]</t>
+  </si>
+  <si>
+    <t>SWITCH (
+    TRUE (),
+    NOT ISBLANK ( [OFFSET-0] ) &amp;&amp; NOT ISBLANK ( [OFFSET-1] ), DIVIDE ( [OFFSET-0], [OFFSET-1] ) - 1
+)</t>
+  </si>
+  <si>
+    <t>0.0%;-0.0%;0.0%</t>
+  </si>
+  <si>
+    <t>WINDOW DELTA</t>
+  </si>
+  <si>
+    <t>[Measures].[WINDOW DELTA]</t>
+  </si>
+  <si>
+    <t>[WINDOW -0] - [WINDOW -1]</t>
+  </si>
+  <si>
+    <t>WINDOW EVO</t>
+  </si>
+  <si>
+    <t>[Measures].[WINDOW EVO]</t>
+  </si>
+  <si>
+    <t>SWITCH (
+    TRUE (),
+    NOT ISBLANK ( [WINDOW -0] ) &amp;&amp; NOT ISBLANK ( [WINDOW -1] ), DIVIDE ( [WINDOW -0], [WINDOW -1] ) - 1
+)</t>
+  </si>
+  <si>
+    <t>WINDOW-YTD</t>
+  </si>
+  <si>
+    <t>[Measures].[WINDOW-YTD]</t>
+  </si>
+  <si>
+    <t>CALCULATE (
+    [__profit],
+    WINDOW (
+        0,
+        ABS,
+        0,
+        REL,
+        SUMMARIZE ( ALLSELECTED ( 'Date' ), 'Date'[Date] ),
+        ORDERBY ( 'Date'[Date], ASC )
+    )
+)</t>
+  </si>
+  <si>
+    <t>NDF_KPI</t>
+  </si>
+  <si>
+    <t>[Measures].[NDF_KPI]</t>
+  </si>
+  <si>
+    <t>NDF_PL (profit)</t>
+  </si>
+  <si>
+    <t>[Measures].[NDF_PL (profit)]</t>
+  </si>
+  <si>
+    <t>NDF_PL %</t>
+  </si>
+  <si>
+    <t>[Measures].[NDF_PL %]</t>
+  </si>
+  <si>
+    <t>__PREV_MONTH</t>
+  </si>
+  <si>
+    <t>[Measures].[__PREV_MONTH]</t>
+  </si>
+  <si>
+    <t>VAR __PREV_MONTH =
+    CALCULATE ( [__profit], DATEADD ( 'Date'[Date], -1, MONTH ) )
+RETURN
+    __PREV_MONTH</t>
+  </si>
+  <si>
+    <t>IBCS</t>
+  </si>
+  <si>
+    <t>#,0</t>
+  </si>
+  <si>
+    <t>__placeholder</t>
+  </si>
+  <si>
+    <t>[Measures].[__placeholder]</t>
+  </si>
+  <si>
+    <t>[__profit]</t>
+  </si>
+  <si>
+    <t>__pos or neg</t>
+  </si>
+  <si>
+    <t>[Measures].[__pos or neg]</t>
+  </si>
+  <si>
+    <t>VAR __curr = [__profit]
+VAR __prev = [__PREV_MONTH]
+VAR Result =
+    SWITCH ( TRUE (), __curr &gt; __prev, __curr, __prev )
+RETURN
+    Result</t>
+  </si>
+  <si>
+    <t>__ibcs (detail)</t>
+  </si>
+  <si>
+    <t>[Measures].[__ibcs (detail)]</t>
+  </si>
+  <si>
+    <t>SWITCH (
+    TRUE (),
+    NOT ISBLANK ( [__PREV_MONTH] ), FORMAT ( DIVIDE ( [__profit], [__PREV_MONTH] ) - 1, "0.0%" )
+) &amp; " | "
+    &amp; SWITCH (
+        TRUE (),
+        NOT ISBLANK ( [__PREV_MONTH] )
+            &amp;&amp; DIVIDE ( [__profit], [__PREV_MONTH] ) - 1 &gt; 0, "🔼",
+        NOT ISBLANK ( [__PREV_MONTH] )
+            &amp;&amp; DIVIDE ( [__profit], [__PREV_MONTH] ) - 1 &lt; 0, "🔽",
+        BLANK ()
+    )</t>
+  </si>
+  <si>
+    <t>__ibcs (custom title)</t>
+  </si>
+  <si>
+    <t>[Measures].[__ibcs (custom title)]</t>
+  </si>
+  <si>
+    <t>FORMAT ( [__profit], "#,,#,K" ) &amp; " | "
+    &amp; FORMAT ( [__PREV_MONTH], "#,,#,K" )</t>
+  </si>
+  <si>
     <t>_ShowValueForDates</t>
   </si>
   <si>
@@ -4141,10 +4535,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U207"/>
+  <dimension ref="A1:U227"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.21875" bestFit="1" customWidth="1"/>
@@ -11643,7 +12037,7 @@
         <v>471</v>
       </c>
       <c r="U141" t="s">
-        <v>472</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
@@ -11654,40 +12048,40 @@
         <v>22</v>
       </c>
       <c r="D142" t="s">
+        <v>472</v>
+      </c>
+      <c r="E142" t="s">
         <v>473</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
+        <v>472</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142" t="s">
+        <v>25</v>
+      </c>
+      <c r="J142" t="s">
+        <v>26</v>
+      </c>
+      <c r="K142" t="s">
+        <v>27</v>
+      </c>
+      <c r="M142" t="s">
+        <v>28</v>
+      </c>
+      <c r="N142" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="F142" t="s">
-        <v>473</v>
-      </c>
-      <c r="H142">
-        <v>0</v>
-      </c>
-      <c r="I142" t="s">
-        <v>25</v>
-      </c>
-      <c r="J142" t="s">
-        <v>26</v>
-      </c>
-      <c r="K142" t="s">
-        <v>27</v>
-      </c>
-      <c r="M142" t="s">
-        <v>28</v>
-      </c>
-      <c r="N142" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="O142" t="s">
         <v>30</v>
       </c>
       <c r="Q142" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="R142" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="S142" t="s">
         <v>31</v>
@@ -11696,7 +12090,7 @@
         <v>471</v>
       </c>
       <c r="U142" t="s">
-        <v>472</v>
+        <v>32</v>
       </c>
     </row>
     <row r="143" spans="1:21" ht="144" x14ac:dyDescent="0.3">
@@ -11707,40 +12101,40 @@
         <v>22</v>
       </c>
       <c r="D143" t="s">
+        <v>475</v>
+      </c>
+      <c r="E143" t="s">
         <v>476</v>
       </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
+        <v>475</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143" t="s">
+        <v>25</v>
+      </c>
+      <c r="J143" t="s">
+        <v>26</v>
+      </c>
+      <c r="K143" t="s">
+        <v>27</v>
+      </c>
+      <c r="M143" t="s">
+        <v>28</v>
+      </c>
+      <c r="N143" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="F143" t="s">
-        <v>476</v>
-      </c>
-      <c r="H143">
-        <v>0</v>
-      </c>
-      <c r="I143" t="s">
-        <v>25</v>
-      </c>
-      <c r="J143" t="s">
-        <v>26</v>
-      </c>
-      <c r="K143" t="s">
-        <v>27</v>
-      </c>
-      <c r="M143" t="s">
-        <v>28</v>
-      </c>
-      <c r="N143" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="O143" t="s">
         <v>30</v>
       </c>
       <c r="Q143" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R143" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="S143" t="s">
         <v>31</v>
@@ -11749,7 +12143,7 @@
         <v>471</v>
       </c>
       <c r="U143" t="s">
-        <v>472</v>
+        <v>32</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.3">
@@ -11760,40 +12154,40 @@
         <v>22</v>
       </c>
       <c r="D144" t="s">
+        <v>478</v>
+      </c>
+      <c r="E144" t="s">
         <v>479</v>
       </c>
-      <c r="E144" t="s">
+      <c r="F144" t="s">
+        <v>478</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144" t="s">
+        <v>25</v>
+      </c>
+      <c r="J144" t="s">
+        <v>26</v>
+      </c>
+      <c r="K144" t="s">
+        <v>27</v>
+      </c>
+      <c r="M144" t="s">
+        <v>28</v>
+      </c>
+      <c r="N144" t="s">
         <v>480</v>
       </c>
-      <c r="F144" t="s">
-        <v>479</v>
-      </c>
-      <c r="H144">
-        <v>0</v>
-      </c>
-      <c r="I144" t="s">
-        <v>25</v>
-      </c>
-      <c r="J144" t="s">
-        <v>26</v>
-      </c>
-      <c r="K144" t="s">
-        <v>27</v>
-      </c>
-      <c r="M144" t="s">
-        <v>28</v>
-      </c>
-      <c r="N144" t="s">
-        <v>481</v>
-      </c>
       <c r="O144" t="s">
         <v>30</v>
       </c>
       <c r="Q144" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="R144" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="S144" t="s">
         <v>31</v>
@@ -11813,46 +12207,46 @@
         <v>22</v>
       </c>
       <c r="D145" t="s">
+        <v>481</v>
+      </c>
+      <c r="E145" t="s">
         <v>482</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" t="s">
+        <v>481</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145" t="s">
+        <v>25</v>
+      </c>
+      <c r="J145" t="s">
+        <v>26</v>
+      </c>
+      <c r="K145" t="s">
+        <v>27</v>
+      </c>
+      <c r="M145" t="s">
+        <v>28</v>
+      </c>
+      <c r="N145" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F145" t="s">
-        <v>482</v>
-      </c>
-      <c r="H145">
-        <v>0</v>
-      </c>
-      <c r="I145" t="s">
-        <v>25</v>
-      </c>
-      <c r="J145" t="s">
-        <v>26</v>
-      </c>
-      <c r="K145" t="s">
-        <v>27</v>
-      </c>
-      <c r="M145" t="s">
-        <v>28</v>
-      </c>
-      <c r="N145" s="2" t="s">
+      <c r="O145" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>481</v>
+      </c>
+      <c r="R145" t="s">
+        <v>481</v>
+      </c>
+      <c r="S145" t="s">
+        <v>31</v>
+      </c>
+      <c r="T145" t="s">
         <v>484</v>
-      </c>
-      <c r="O145" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q145" t="s">
-        <v>482</v>
-      </c>
-      <c r="R145" t="s">
-        <v>482</v>
-      </c>
-      <c r="S145" t="s">
-        <v>31</v>
-      </c>
-      <c r="T145" t="s">
-        <v>485</v>
       </c>
       <c r="U145" t="s">
         <v>32</v>
@@ -11866,46 +12260,46 @@
         <v>22</v>
       </c>
       <c r="D146" t="s">
+        <v>485</v>
+      </c>
+      <c r="E146" t="s">
         <v>486</v>
       </c>
-      <c r="E146" t="s">
+      <c r="F146" t="s">
+        <v>485</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146" t="s">
+        <v>25</v>
+      </c>
+      <c r="J146" t="s">
+        <v>26</v>
+      </c>
+      <c r="K146" t="s">
+        <v>27</v>
+      </c>
+      <c r="M146" t="s">
+        <v>28</v>
+      </c>
+      <c r="N146" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="F146" t="s">
-        <v>486</v>
-      </c>
-      <c r="H146">
-        <v>0</v>
-      </c>
-      <c r="I146" t="s">
-        <v>25</v>
-      </c>
-      <c r="J146" t="s">
-        <v>26</v>
-      </c>
-      <c r="K146" t="s">
-        <v>27</v>
-      </c>
-      <c r="M146" t="s">
-        <v>28</v>
-      </c>
-      <c r="N146" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="O146" t="s">
         <v>30</v>
       </c>
       <c r="Q146" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="R146" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="S146" t="s">
         <v>31</v>
       </c>
       <c r="T146" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="U146" t="s">
         <v>32</v>
@@ -11919,46 +12313,46 @@
         <v>22</v>
       </c>
       <c r="D147" t="s">
+        <v>488</v>
+      </c>
+      <c r="E147" t="s">
         <v>489</v>
       </c>
-      <c r="E147" t="s">
+      <c r="F147" t="s">
+        <v>488</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147" t="s">
+        <v>25</v>
+      </c>
+      <c r="J147" t="s">
+        <v>26</v>
+      </c>
+      <c r="K147" t="s">
+        <v>27</v>
+      </c>
+      <c r="M147" t="s">
+        <v>28</v>
+      </c>
+      <c r="N147" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="F147" t="s">
-        <v>489</v>
-      </c>
-      <c r="H147">
-        <v>0</v>
-      </c>
-      <c r="I147" t="s">
-        <v>25</v>
-      </c>
-      <c r="J147" t="s">
-        <v>26</v>
-      </c>
-      <c r="K147" t="s">
-        <v>27</v>
-      </c>
-      <c r="M147" t="s">
-        <v>28</v>
-      </c>
-      <c r="N147" s="2" t="s">
-        <v>491</v>
-      </c>
       <c r="O147" t="s">
         <v>30</v>
       </c>
       <c r="Q147" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="R147" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="S147" t="s">
         <v>31</v>
       </c>
       <c r="T147" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="U147" t="s">
         <v>32</v>
@@ -11972,46 +12366,46 @@
         <v>22</v>
       </c>
       <c r="D148" t="s">
+        <v>491</v>
+      </c>
+      <c r="E148" t="s">
         <v>492</v>
       </c>
-      <c r="E148" t="s">
+      <c r="F148" t="s">
+        <v>491</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148" t="s">
+        <v>25</v>
+      </c>
+      <c r="J148" t="s">
+        <v>26</v>
+      </c>
+      <c r="K148" t="s">
+        <v>27</v>
+      </c>
+      <c r="M148" t="s">
+        <v>28</v>
+      </c>
+      <c r="N148" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="F148" t="s">
-        <v>492</v>
-      </c>
-      <c r="H148">
-        <v>0</v>
-      </c>
-      <c r="I148" t="s">
-        <v>25</v>
-      </c>
-      <c r="J148" t="s">
-        <v>26</v>
-      </c>
-      <c r="K148" t="s">
-        <v>27</v>
-      </c>
-      <c r="M148" t="s">
-        <v>28</v>
-      </c>
-      <c r="N148" s="2" t="s">
+      <c r="O148" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>491</v>
+      </c>
+      <c r="R148" t="s">
+        <v>491</v>
+      </c>
+      <c r="S148" t="s">
+        <v>31</v>
+      </c>
+      <c r="T148" t="s">
         <v>494</v>
-      </c>
-      <c r="O148" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q148" t="s">
-        <v>492</v>
-      </c>
-      <c r="R148" t="s">
-        <v>492</v>
-      </c>
-      <c r="S148" t="s">
-        <v>31</v>
-      </c>
-      <c r="T148" t="s">
-        <v>495</v>
       </c>
       <c r="U148" t="s">
         <v>32</v>
@@ -12025,46 +12419,46 @@
         <v>22</v>
       </c>
       <c r="D149" t="s">
+        <v>495</v>
+      </c>
+      <c r="E149" t="s">
         <v>496</v>
       </c>
-      <c r="E149" t="s">
+      <c r="F149" t="s">
+        <v>495</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149" t="s">
+        <v>25</v>
+      </c>
+      <c r="J149" t="s">
+        <v>26</v>
+      </c>
+      <c r="K149" t="s">
+        <v>27</v>
+      </c>
+      <c r="M149" t="s">
+        <v>28</v>
+      </c>
+      <c r="N149" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="F149" t="s">
-        <v>496</v>
-      </c>
-      <c r="H149">
-        <v>0</v>
-      </c>
-      <c r="I149" t="s">
-        <v>25</v>
-      </c>
-      <c r="J149" t="s">
-        <v>26</v>
-      </c>
-      <c r="K149" t="s">
-        <v>27</v>
-      </c>
-      <c r="M149" t="s">
-        <v>28</v>
-      </c>
-      <c r="N149" s="2" t="s">
-        <v>498</v>
-      </c>
       <c r="O149" t="s">
         <v>30</v>
       </c>
       <c r="Q149" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="R149" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="S149" t="s">
         <v>31</v>
       </c>
       <c r="T149" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U149" t="s">
         <v>32</v>
@@ -12078,46 +12472,46 @@
         <v>22</v>
       </c>
       <c r="D150" t="s">
+        <v>498</v>
+      </c>
+      <c r="E150" t="s">
         <v>499</v>
       </c>
-      <c r="E150" t="s">
+      <c r="F150" t="s">
+        <v>498</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150" t="s">
+        <v>25</v>
+      </c>
+      <c r="J150" t="s">
+        <v>26</v>
+      </c>
+      <c r="K150" t="s">
+        <v>27</v>
+      </c>
+      <c r="M150" t="s">
+        <v>28</v>
+      </c>
+      <c r="N150" t="s">
         <v>500</v>
       </c>
-      <c r="F150" t="s">
-        <v>499</v>
-      </c>
-      <c r="H150">
-        <v>0</v>
-      </c>
-      <c r="I150" t="s">
-        <v>25</v>
-      </c>
-      <c r="J150" t="s">
-        <v>26</v>
-      </c>
-      <c r="K150" t="s">
-        <v>27</v>
-      </c>
-      <c r="M150" t="s">
-        <v>28</v>
-      </c>
-      <c r="N150" t="s">
-        <v>501</v>
-      </c>
       <c r="O150" t="s">
         <v>30</v>
       </c>
       <c r="Q150" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="R150" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="S150" t="s">
         <v>31</v>
       </c>
       <c r="T150" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U150" t="s">
         <v>72</v>
@@ -12131,46 +12525,46 @@
         <v>22</v>
       </c>
       <c r="D151" t="s">
+        <v>501</v>
+      </c>
+      <c r="E151" t="s">
         <v>502</v>
       </c>
-      <c r="E151" t="s">
+      <c r="F151" t="s">
+        <v>501</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151" t="s">
+        <v>25</v>
+      </c>
+      <c r="J151" t="s">
+        <v>26</v>
+      </c>
+      <c r="K151" t="s">
+        <v>27</v>
+      </c>
+      <c r="M151" t="s">
+        <v>28</v>
+      </c>
+      <c r="N151" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="F151" t="s">
-        <v>502</v>
-      </c>
-      <c r="H151">
-        <v>0</v>
-      </c>
-      <c r="I151" t="s">
-        <v>25</v>
-      </c>
-      <c r="J151" t="s">
-        <v>26</v>
-      </c>
-      <c r="K151" t="s">
-        <v>27</v>
-      </c>
-      <c r="M151" t="s">
-        <v>28</v>
-      </c>
-      <c r="N151" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="O151" t="s">
         <v>30</v>
       </c>
       <c r="Q151" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="R151" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="S151" t="s">
         <v>31</v>
       </c>
       <c r="T151" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U151" t="s">
         <v>32</v>
@@ -12184,46 +12578,46 @@
         <v>22</v>
       </c>
       <c r="D152" t="s">
+        <v>504</v>
+      </c>
+      <c r="E152" t="s">
         <v>505</v>
       </c>
-      <c r="E152" t="s">
+      <c r="F152" t="s">
+        <v>504</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152" t="s">
+        <v>25</v>
+      </c>
+      <c r="J152" t="s">
+        <v>26</v>
+      </c>
+      <c r="K152" t="s">
+        <v>27</v>
+      </c>
+      <c r="M152" t="s">
+        <v>28</v>
+      </c>
+      <c r="N152" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="F152" t="s">
-        <v>505</v>
-      </c>
-      <c r="H152">
-        <v>0</v>
-      </c>
-      <c r="I152" t="s">
-        <v>25</v>
-      </c>
-      <c r="J152" t="s">
-        <v>26</v>
-      </c>
-      <c r="K152" t="s">
-        <v>27</v>
-      </c>
-      <c r="M152" t="s">
-        <v>28</v>
-      </c>
-      <c r="N152" s="2" t="s">
-        <v>507</v>
-      </c>
       <c r="O152" t="s">
         <v>30</v>
       </c>
       <c r="Q152" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="R152" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S152" t="s">
         <v>31</v>
       </c>
       <c r="T152" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U152" t="s">
         <v>32</v>
@@ -12237,46 +12631,46 @@
         <v>22</v>
       </c>
       <c r="D153" t="s">
+        <v>507</v>
+      </c>
+      <c r="E153" t="s">
         <v>508</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" t="s">
+        <v>507</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153" t="s">
+        <v>25</v>
+      </c>
+      <c r="J153" t="s">
+        <v>26</v>
+      </c>
+      <c r="K153" t="s">
+        <v>27</v>
+      </c>
+      <c r="M153" t="s">
+        <v>28</v>
+      </c>
+      <c r="N153" t="s">
         <v>509</v>
       </c>
-      <c r="F153" t="s">
-        <v>508</v>
-      </c>
-      <c r="H153">
-        <v>0</v>
-      </c>
-      <c r="I153" t="s">
-        <v>25</v>
-      </c>
-      <c r="J153" t="s">
-        <v>26</v>
-      </c>
-      <c r="K153" t="s">
-        <v>27</v>
-      </c>
-      <c r="M153" t="s">
-        <v>28</v>
-      </c>
-      <c r="N153" t="s">
-        <v>510</v>
-      </c>
       <c r="O153" t="s">
         <v>30</v>
       </c>
       <c r="Q153" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="R153" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="S153" t="s">
         <v>31</v>
       </c>
       <c r="T153" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U153" t="s">
         <v>72</v>
@@ -12290,46 +12684,46 @@
         <v>22</v>
       </c>
       <c r="D154" t="s">
+        <v>510</v>
+      </c>
+      <c r="E154" t="s">
         <v>511</v>
       </c>
-      <c r="E154" t="s">
+      <c r="F154" t="s">
+        <v>510</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154" t="s">
+        <v>25</v>
+      </c>
+      <c r="J154" t="s">
+        <v>26</v>
+      </c>
+      <c r="K154" t="s">
+        <v>27</v>
+      </c>
+      <c r="M154" t="s">
+        <v>28</v>
+      </c>
+      <c r="N154" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="F154" t="s">
-        <v>511</v>
-      </c>
-      <c r="H154">
-        <v>0</v>
-      </c>
-      <c r="I154" t="s">
-        <v>25</v>
-      </c>
-      <c r="J154" t="s">
-        <v>26</v>
-      </c>
-      <c r="K154" t="s">
-        <v>27</v>
-      </c>
-      <c r="M154" t="s">
-        <v>28</v>
-      </c>
-      <c r="N154" s="2" t="s">
-        <v>513</v>
-      </c>
       <c r="O154" t="s">
         <v>30</v>
       </c>
       <c r="Q154" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R154" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="S154" t="s">
         <v>31</v>
       </c>
       <c r="T154" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U154" t="s">
         <v>32</v>
@@ -12343,46 +12737,46 @@
         <v>22</v>
       </c>
       <c r="D155" t="s">
+        <v>513</v>
+      </c>
+      <c r="E155" t="s">
         <v>514</v>
       </c>
-      <c r="E155" t="s">
+      <c r="F155" t="s">
+        <v>513</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155" t="s">
+        <v>25</v>
+      </c>
+      <c r="J155" t="s">
+        <v>26</v>
+      </c>
+      <c r="K155" t="s">
+        <v>27</v>
+      </c>
+      <c r="M155" t="s">
+        <v>28</v>
+      </c>
+      <c r="N155" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="F155" t="s">
-        <v>514</v>
-      </c>
-      <c r="H155">
-        <v>0</v>
-      </c>
-      <c r="I155" t="s">
-        <v>25</v>
-      </c>
-      <c r="J155" t="s">
-        <v>26</v>
-      </c>
-      <c r="K155" t="s">
-        <v>27</v>
-      </c>
-      <c r="M155" t="s">
-        <v>28</v>
-      </c>
-      <c r="N155" s="2" t="s">
-        <v>516</v>
-      </c>
       <c r="O155" t="s">
         <v>30</v>
       </c>
       <c r="Q155" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R155" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S155" t="s">
         <v>31</v>
       </c>
       <c r="T155" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U155" t="s">
         <v>32</v>
@@ -12396,46 +12790,46 @@
         <v>22</v>
       </c>
       <c r="D156" t="s">
+        <v>516</v>
+      </c>
+      <c r="E156" t="s">
         <v>517</v>
       </c>
-      <c r="E156" t="s">
+      <c r="F156" t="s">
+        <v>516</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156" t="s">
+        <v>25</v>
+      </c>
+      <c r="J156" t="s">
+        <v>26</v>
+      </c>
+      <c r="K156" t="s">
+        <v>27</v>
+      </c>
+      <c r="M156" t="s">
+        <v>28</v>
+      </c>
+      <c r="N156" t="s">
         <v>518</v>
       </c>
-      <c r="F156" t="s">
-        <v>517</v>
-      </c>
-      <c r="H156">
-        <v>0</v>
-      </c>
-      <c r="I156" t="s">
-        <v>25</v>
-      </c>
-      <c r="J156" t="s">
-        <v>26</v>
-      </c>
-      <c r="K156" t="s">
-        <v>27</v>
-      </c>
-      <c r="M156" t="s">
-        <v>28</v>
-      </c>
-      <c r="N156" t="s">
-        <v>519</v>
-      </c>
       <c r="O156" t="s">
         <v>30</v>
       </c>
       <c r="Q156" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="R156" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S156" t="s">
         <v>31</v>
       </c>
       <c r="T156" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U156" t="s">
         <v>72</v>
@@ -12449,46 +12843,46 @@
         <v>22</v>
       </c>
       <c r="D157" t="s">
+        <v>519</v>
+      </c>
+      <c r="E157" t="s">
         <v>520</v>
       </c>
-      <c r="E157" t="s">
+      <c r="F157" t="s">
+        <v>519</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157" t="s">
+        <v>25</v>
+      </c>
+      <c r="J157" t="s">
+        <v>26</v>
+      </c>
+      <c r="K157" t="s">
+        <v>27</v>
+      </c>
+      <c r="M157" t="s">
+        <v>28</v>
+      </c>
+      <c r="N157" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="F157" t="s">
-        <v>520</v>
-      </c>
-      <c r="H157">
-        <v>0</v>
-      </c>
-      <c r="I157" t="s">
-        <v>25</v>
-      </c>
-      <c r="J157" t="s">
-        <v>26</v>
-      </c>
-      <c r="K157" t="s">
-        <v>27</v>
-      </c>
-      <c r="M157" t="s">
-        <v>28</v>
-      </c>
-      <c r="N157" s="2" t="s">
+      <c r="O157" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>519</v>
+      </c>
+      <c r="R157" t="s">
+        <v>519</v>
+      </c>
+      <c r="S157" t="s">
+        <v>31</v>
+      </c>
+      <c r="T157" t="s">
         <v>522</v>
-      </c>
-      <c r="O157" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q157" t="s">
-        <v>520</v>
-      </c>
-      <c r="R157" t="s">
-        <v>520</v>
-      </c>
-      <c r="S157" t="s">
-        <v>31</v>
-      </c>
-      <c r="T157" t="s">
-        <v>523</v>
       </c>
       <c r="U157" t="s">
         <v>32</v>
@@ -12502,46 +12896,46 @@
         <v>22</v>
       </c>
       <c r="D158" t="s">
+        <v>523</v>
+      </c>
+      <c r="E158" t="s">
         <v>524</v>
       </c>
-      <c r="E158" t="s">
+      <c r="F158" t="s">
+        <v>523</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158" t="s">
+        <v>25</v>
+      </c>
+      <c r="J158" t="s">
+        <v>26</v>
+      </c>
+      <c r="K158" t="s">
+        <v>27</v>
+      </c>
+      <c r="M158" t="s">
+        <v>28</v>
+      </c>
+      <c r="N158" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="F158" t="s">
-        <v>524</v>
-      </c>
-      <c r="H158">
-        <v>0</v>
-      </c>
-      <c r="I158" t="s">
-        <v>25</v>
-      </c>
-      <c r="J158" t="s">
-        <v>26</v>
-      </c>
-      <c r="K158" t="s">
-        <v>27</v>
-      </c>
-      <c r="M158" t="s">
-        <v>28</v>
-      </c>
-      <c r="N158" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="O158" t="s">
         <v>30</v>
       </c>
       <c r="Q158" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="R158" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="S158" t="s">
         <v>31</v>
       </c>
       <c r="T158" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="U158" t="s">
         <v>32</v>
@@ -12555,46 +12949,46 @@
         <v>22</v>
       </c>
       <c r="D159" t="s">
+        <v>526</v>
+      </c>
+      <c r="E159" t="s">
         <v>527</v>
       </c>
-      <c r="E159" t="s">
+      <c r="F159" t="s">
+        <v>526</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159" t="s">
+        <v>25</v>
+      </c>
+      <c r="J159" t="s">
+        <v>26</v>
+      </c>
+      <c r="K159" t="s">
+        <v>27</v>
+      </c>
+      <c r="M159" t="s">
+        <v>28</v>
+      </c>
+      <c r="N159" t="s">
         <v>528</v>
       </c>
-      <c r="F159" t="s">
-        <v>527</v>
-      </c>
-      <c r="H159">
-        <v>0</v>
-      </c>
-      <c r="I159" t="s">
-        <v>25</v>
-      </c>
-      <c r="J159" t="s">
-        <v>26</v>
-      </c>
-      <c r="K159" t="s">
-        <v>27</v>
-      </c>
-      <c r="M159" t="s">
-        <v>28</v>
-      </c>
-      <c r="N159" t="s">
-        <v>529</v>
-      </c>
       <c r="O159" t="s">
         <v>30</v>
       </c>
       <c r="Q159" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="R159" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="S159" t="s">
         <v>31</v>
       </c>
       <c r="T159" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="U159" t="s">
         <v>72</v>
@@ -12608,46 +13002,46 @@
         <v>22</v>
       </c>
       <c r="D160" t="s">
+        <v>529</v>
+      </c>
+      <c r="E160" t="s">
         <v>530</v>
       </c>
-      <c r="E160" t="s">
+      <c r="F160" t="s">
+        <v>529</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160" t="s">
+        <v>25</v>
+      </c>
+      <c r="J160" t="s">
+        <v>26</v>
+      </c>
+      <c r="K160" t="s">
+        <v>27</v>
+      </c>
+      <c r="M160" t="s">
+        <v>28</v>
+      </c>
+      <c r="N160" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="F160" t="s">
-        <v>530</v>
-      </c>
-      <c r="H160">
-        <v>0</v>
-      </c>
-      <c r="I160" t="s">
-        <v>25</v>
-      </c>
-      <c r="J160" t="s">
-        <v>26</v>
-      </c>
-      <c r="K160" t="s">
-        <v>27</v>
-      </c>
-      <c r="M160" t="s">
-        <v>28</v>
-      </c>
-      <c r="N160" s="2" t="s">
-        <v>532</v>
-      </c>
       <c r="O160" t="s">
         <v>30</v>
       </c>
       <c r="Q160" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="R160" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="S160" t="s">
         <v>31</v>
       </c>
       <c r="T160" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="U160" t="s">
         <v>32</v>
@@ -12661,46 +13055,46 @@
         <v>22</v>
       </c>
       <c r="D161" t="s">
+        <v>532</v>
+      </c>
+      <c r="E161" t="s">
         <v>533</v>
       </c>
-      <c r="E161" t="s">
+      <c r="F161" t="s">
+        <v>532</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161" t="s">
+        <v>25</v>
+      </c>
+      <c r="J161" t="s">
+        <v>26</v>
+      </c>
+      <c r="K161" t="s">
+        <v>27</v>
+      </c>
+      <c r="M161" t="s">
+        <v>28</v>
+      </c>
+      <c r="N161" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="F161" t="s">
-        <v>533</v>
-      </c>
-      <c r="H161">
-        <v>0</v>
-      </c>
-      <c r="I161" t="s">
-        <v>25</v>
-      </c>
-      <c r="J161" t="s">
-        <v>26</v>
-      </c>
-      <c r="K161" t="s">
-        <v>27</v>
-      </c>
-      <c r="M161" t="s">
-        <v>28</v>
-      </c>
-      <c r="N161" s="2" t="s">
-        <v>535</v>
-      </c>
       <c r="O161" t="s">
         <v>30</v>
       </c>
       <c r="Q161" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="R161" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="S161" t="s">
         <v>31</v>
       </c>
       <c r="T161" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="U161" t="s">
         <v>32</v>
@@ -12714,46 +13108,46 @@
         <v>22</v>
       </c>
       <c r="D162" t="s">
+        <v>535</v>
+      </c>
+      <c r="E162" t="s">
         <v>536</v>
       </c>
-      <c r="E162" t="s">
+      <c r="F162" t="s">
+        <v>535</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162" t="s">
+        <v>25</v>
+      </c>
+      <c r="J162" t="s">
+        <v>26</v>
+      </c>
+      <c r="K162" t="s">
+        <v>27</v>
+      </c>
+      <c r="M162" t="s">
+        <v>28</v>
+      </c>
+      <c r="N162" t="s">
         <v>537</v>
       </c>
-      <c r="F162" t="s">
-        <v>536</v>
-      </c>
-      <c r="H162">
-        <v>0</v>
-      </c>
-      <c r="I162" t="s">
-        <v>25</v>
-      </c>
-      <c r="J162" t="s">
-        <v>26</v>
-      </c>
-      <c r="K162" t="s">
-        <v>27</v>
-      </c>
-      <c r="M162" t="s">
-        <v>28</v>
-      </c>
-      <c r="N162" t="s">
-        <v>538</v>
-      </c>
       <c r="O162" t="s">
         <v>30</v>
       </c>
       <c r="Q162" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="R162" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="S162" t="s">
         <v>31</v>
       </c>
       <c r="T162" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="U162" t="s">
         <v>72</v>
@@ -12767,46 +13161,46 @@
         <v>22</v>
       </c>
       <c r="D163" t="s">
+        <v>538</v>
+      </c>
+      <c r="E163" t="s">
         <v>539</v>
       </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
+        <v>538</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163" t="s">
+        <v>25</v>
+      </c>
+      <c r="J163" t="s">
+        <v>26</v>
+      </c>
+      <c r="K163" t="s">
+        <v>27</v>
+      </c>
+      <c r="M163" t="s">
+        <v>28</v>
+      </c>
+      <c r="N163" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="F163" t="s">
-        <v>539</v>
-      </c>
-      <c r="H163">
-        <v>0</v>
-      </c>
-      <c r="I163" t="s">
-        <v>25</v>
-      </c>
-      <c r="J163" t="s">
-        <v>26</v>
-      </c>
-      <c r="K163" t="s">
-        <v>27</v>
-      </c>
-      <c r="M163" t="s">
-        <v>28</v>
-      </c>
-      <c r="N163" s="2" t="s">
-        <v>541</v>
-      </c>
       <c r="O163" t="s">
         <v>30</v>
       </c>
       <c r="Q163" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="R163" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="S163" t="s">
         <v>31</v>
       </c>
       <c r="T163" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="U163" t="s">
         <v>32</v>
@@ -12820,46 +13214,46 @@
         <v>22</v>
       </c>
       <c r="D164" t="s">
+        <v>541</v>
+      </c>
+      <c r="E164" t="s">
         <v>542</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
+        <v>541</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164" t="s">
+        <v>25</v>
+      </c>
+      <c r="J164" t="s">
+        <v>26</v>
+      </c>
+      <c r="K164" t="s">
+        <v>27</v>
+      </c>
+      <c r="M164" t="s">
+        <v>28</v>
+      </c>
+      <c r="N164" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="F164" t="s">
-        <v>542</v>
-      </c>
-      <c r="H164">
-        <v>0</v>
-      </c>
-      <c r="I164" t="s">
-        <v>25</v>
-      </c>
-      <c r="J164" t="s">
-        <v>26</v>
-      </c>
-      <c r="K164" t="s">
-        <v>27</v>
-      </c>
-      <c r="M164" t="s">
-        <v>28</v>
-      </c>
-      <c r="N164" s="2" t="s">
-        <v>544</v>
-      </c>
       <c r="O164" t="s">
         <v>30</v>
       </c>
       <c r="Q164" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="R164" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="S164" t="s">
         <v>31</v>
       </c>
       <c r="T164" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="U164" t="s">
         <v>32</v>
@@ -12873,46 +13267,46 @@
         <v>22</v>
       </c>
       <c r="D165" t="s">
+        <v>544</v>
+      </c>
+      <c r="E165" t="s">
         <v>545</v>
       </c>
-      <c r="E165" t="s">
+      <c r="F165" t="s">
+        <v>544</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165" t="s">
+        <v>25</v>
+      </c>
+      <c r="J165" t="s">
+        <v>26</v>
+      </c>
+      <c r="K165" t="s">
+        <v>27</v>
+      </c>
+      <c r="M165" t="s">
+        <v>28</v>
+      </c>
+      <c r="N165" t="s">
         <v>546</v>
       </c>
-      <c r="F165" t="s">
-        <v>545</v>
-      </c>
-      <c r="H165">
-        <v>0</v>
-      </c>
-      <c r="I165" t="s">
-        <v>25</v>
-      </c>
-      <c r="J165" t="s">
-        <v>26</v>
-      </c>
-      <c r="K165" t="s">
-        <v>27</v>
-      </c>
-      <c r="M165" t="s">
-        <v>28</v>
-      </c>
-      <c r="N165" t="s">
-        <v>547</v>
-      </c>
       <c r="O165" t="s">
         <v>30</v>
       </c>
       <c r="Q165" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="R165" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="S165" t="s">
         <v>31</v>
       </c>
       <c r="T165" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="U165" t="s">
         <v>72</v>
@@ -12926,46 +13320,46 @@
         <v>22</v>
       </c>
       <c r="D166" t="s">
+        <v>547</v>
+      </c>
+      <c r="E166" t="s">
         <v>548</v>
       </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
+        <v>547</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166" t="s">
+        <v>25</v>
+      </c>
+      <c r="J166" t="s">
+        <v>26</v>
+      </c>
+      <c r="K166" t="s">
+        <v>27</v>
+      </c>
+      <c r="M166" t="s">
+        <v>28</v>
+      </c>
+      <c r="N166" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="F166" t="s">
-        <v>548</v>
-      </c>
-      <c r="H166">
-        <v>0</v>
-      </c>
-      <c r="I166" t="s">
-        <v>25</v>
-      </c>
-      <c r="J166" t="s">
-        <v>26</v>
-      </c>
-      <c r="K166" t="s">
-        <v>27</v>
-      </c>
-      <c r="M166" t="s">
-        <v>28</v>
-      </c>
-      <c r="N166" s="2" t="s">
+      <c r="O166" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>547</v>
+      </c>
+      <c r="R166" t="s">
+        <v>547</v>
+      </c>
+      <c r="S166" t="s">
+        <v>31</v>
+      </c>
+      <c r="T166" t="s">
         <v>550</v>
-      </c>
-      <c r="O166" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q166" t="s">
-        <v>548</v>
-      </c>
-      <c r="R166" t="s">
-        <v>548</v>
-      </c>
-      <c r="S166" t="s">
-        <v>31</v>
-      </c>
-      <c r="T166" t="s">
-        <v>551</v>
       </c>
       <c r="U166" t="s">
         <v>32</v>
@@ -12979,46 +13373,46 @@
         <v>22</v>
       </c>
       <c r="D167" t="s">
+        <v>551</v>
+      </c>
+      <c r="E167" t="s">
         <v>552</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" t="s">
+        <v>551</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167" t="s">
+        <v>25</v>
+      </c>
+      <c r="J167" t="s">
+        <v>26</v>
+      </c>
+      <c r="K167" t="s">
+        <v>27</v>
+      </c>
+      <c r="M167" t="s">
+        <v>28</v>
+      </c>
+      <c r="N167" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="F167" t="s">
-        <v>552</v>
-      </c>
-      <c r="H167">
-        <v>0</v>
-      </c>
-      <c r="I167" t="s">
-        <v>25</v>
-      </c>
-      <c r="J167" t="s">
-        <v>26</v>
-      </c>
-      <c r="K167" t="s">
-        <v>27</v>
-      </c>
-      <c r="M167" t="s">
-        <v>28</v>
-      </c>
-      <c r="N167" s="2" t="s">
-        <v>554</v>
-      </c>
       <c r="O167" t="s">
         <v>30</v>
       </c>
       <c r="Q167" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="R167" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="S167" t="s">
         <v>31</v>
       </c>
       <c r="T167" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U167" t="s">
         <v>32</v>
@@ -13032,46 +13426,46 @@
         <v>22</v>
       </c>
       <c r="D168" t="s">
+        <v>554</v>
+      </c>
+      <c r="E168" t="s">
         <v>555</v>
       </c>
-      <c r="E168" t="s">
+      <c r="F168" t="s">
+        <v>554</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168" t="s">
+        <v>25</v>
+      </c>
+      <c r="J168" t="s">
+        <v>26</v>
+      </c>
+      <c r="K168" t="s">
+        <v>27</v>
+      </c>
+      <c r="M168" t="s">
+        <v>28</v>
+      </c>
+      <c r="N168" t="s">
         <v>556</v>
       </c>
-      <c r="F168" t="s">
-        <v>555</v>
-      </c>
-      <c r="H168">
-        <v>0</v>
-      </c>
-      <c r="I168" t="s">
-        <v>25</v>
-      </c>
-      <c r="J168" t="s">
-        <v>26</v>
-      </c>
-      <c r="K168" t="s">
-        <v>27</v>
-      </c>
-      <c r="M168" t="s">
-        <v>28</v>
-      </c>
-      <c r="N168" t="s">
-        <v>557</v>
-      </c>
       <c r="O168" t="s">
         <v>30</v>
       </c>
       <c r="Q168" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="R168" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="S168" t="s">
         <v>31</v>
       </c>
       <c r="T168" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U168" t="s">
         <v>72</v>
@@ -13085,46 +13479,46 @@
         <v>22</v>
       </c>
       <c r="D169" t="s">
+        <v>557</v>
+      </c>
+      <c r="E169" t="s">
         <v>558</v>
       </c>
-      <c r="E169" t="s">
+      <c r="F169" t="s">
+        <v>557</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169" t="s">
+        <v>25</v>
+      </c>
+      <c r="J169" t="s">
+        <v>26</v>
+      </c>
+      <c r="K169" t="s">
+        <v>27</v>
+      </c>
+      <c r="M169" t="s">
+        <v>28</v>
+      </c>
+      <c r="N169" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="F169" t="s">
-        <v>558</v>
-      </c>
-      <c r="H169">
-        <v>0</v>
-      </c>
-      <c r="I169" t="s">
-        <v>25</v>
-      </c>
-      <c r="J169" t="s">
-        <v>26</v>
-      </c>
-      <c r="K169" t="s">
-        <v>27</v>
-      </c>
-      <c r="M169" t="s">
-        <v>28</v>
-      </c>
-      <c r="N169" s="2" t="s">
-        <v>560</v>
-      </c>
       <c r="O169" t="s">
         <v>30</v>
       </c>
       <c r="Q169" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="R169" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="S169" t="s">
         <v>31</v>
       </c>
       <c r="T169" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U169" t="s">
         <v>32</v>
@@ -13138,46 +13532,46 @@
         <v>22</v>
       </c>
       <c r="D170" t="s">
+        <v>560</v>
+      </c>
+      <c r="E170" t="s">
         <v>561</v>
       </c>
-      <c r="E170" t="s">
+      <c r="F170" t="s">
+        <v>560</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170" t="s">
+        <v>25</v>
+      </c>
+      <c r="J170" t="s">
+        <v>26</v>
+      </c>
+      <c r="K170" t="s">
+        <v>27</v>
+      </c>
+      <c r="M170" t="s">
+        <v>28</v>
+      </c>
+      <c r="N170" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="F170" t="s">
-        <v>561</v>
-      </c>
-      <c r="H170">
-        <v>0</v>
-      </c>
-      <c r="I170" t="s">
-        <v>25</v>
-      </c>
-      <c r="J170" t="s">
-        <v>26</v>
-      </c>
-      <c r="K170" t="s">
-        <v>27</v>
-      </c>
-      <c r="M170" t="s">
-        <v>28</v>
-      </c>
-      <c r="N170" s="2" t="s">
-        <v>563</v>
-      </c>
       <c r="O170" t="s">
         <v>30</v>
       </c>
       <c r="Q170" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="R170" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="S170" t="s">
         <v>31</v>
       </c>
       <c r="T170" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U170" t="s">
         <v>32</v>
@@ -13191,46 +13585,46 @@
         <v>22</v>
       </c>
       <c r="D171" t="s">
+        <v>563</v>
+      </c>
+      <c r="E171" t="s">
         <v>564</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
+        <v>563</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171" t="s">
+        <v>25</v>
+      </c>
+      <c r="J171" t="s">
+        <v>26</v>
+      </c>
+      <c r="K171" t="s">
+        <v>27</v>
+      </c>
+      <c r="M171" t="s">
+        <v>28</v>
+      </c>
+      <c r="N171" t="s">
         <v>565</v>
       </c>
-      <c r="F171" t="s">
-        <v>564</v>
-      </c>
-      <c r="H171">
-        <v>0</v>
-      </c>
-      <c r="I171" t="s">
-        <v>25</v>
-      </c>
-      <c r="J171" t="s">
-        <v>26</v>
-      </c>
-      <c r="K171" t="s">
-        <v>27</v>
-      </c>
-      <c r="M171" t="s">
-        <v>28</v>
-      </c>
-      <c r="N171" t="s">
-        <v>566</v>
-      </c>
       <c r="O171" t="s">
         <v>30</v>
       </c>
       <c r="Q171" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="R171" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="S171" t="s">
         <v>31</v>
       </c>
       <c r="T171" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U171" t="s">
         <v>72</v>
@@ -13244,46 +13638,46 @@
         <v>22</v>
       </c>
       <c r="D172" t="s">
+        <v>566</v>
+      </c>
+      <c r="E172" t="s">
         <v>567</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
+        <v>566</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172" t="s">
+        <v>25</v>
+      </c>
+      <c r="J172" t="s">
+        <v>26</v>
+      </c>
+      <c r="K172" t="s">
+        <v>27</v>
+      </c>
+      <c r="M172" t="s">
+        <v>28</v>
+      </c>
+      <c r="N172" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="F172" t="s">
-        <v>567</v>
-      </c>
-      <c r="H172">
-        <v>0</v>
-      </c>
-      <c r="I172" t="s">
-        <v>25</v>
-      </c>
-      <c r="J172" t="s">
-        <v>26</v>
-      </c>
-      <c r="K172" t="s">
-        <v>27</v>
-      </c>
-      <c r="M172" t="s">
-        <v>28</v>
-      </c>
-      <c r="N172" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="O172" t="s">
         <v>30</v>
       </c>
       <c r="Q172" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="R172" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="S172" t="s">
         <v>31</v>
       </c>
       <c r="T172" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U172" t="s">
         <v>32</v>
@@ -13297,46 +13691,46 @@
         <v>22</v>
       </c>
       <c r="D173" t="s">
+        <v>569</v>
+      </c>
+      <c r="E173" t="s">
         <v>570</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
+        <v>569</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173" t="s">
+        <v>25</v>
+      </c>
+      <c r="J173" t="s">
+        <v>26</v>
+      </c>
+      <c r="K173" t="s">
+        <v>27</v>
+      </c>
+      <c r="M173" t="s">
+        <v>28</v>
+      </c>
+      <c r="N173" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="F173" t="s">
-        <v>570</v>
-      </c>
-      <c r="H173">
-        <v>0</v>
-      </c>
-      <c r="I173" t="s">
-        <v>25</v>
-      </c>
-      <c r="J173" t="s">
-        <v>26</v>
-      </c>
-      <c r="K173" t="s">
-        <v>27</v>
-      </c>
-      <c r="M173" t="s">
-        <v>28</v>
-      </c>
-      <c r="N173" s="2" t="s">
-        <v>572</v>
-      </c>
       <c r="O173" t="s">
         <v>30</v>
       </c>
       <c r="Q173" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="R173" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="S173" t="s">
         <v>31</v>
       </c>
       <c r="T173" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U173" t="s">
         <v>32</v>
@@ -13350,46 +13744,46 @@
         <v>22</v>
       </c>
       <c r="D174" t="s">
+        <v>572</v>
+      </c>
+      <c r="E174" t="s">
         <v>573</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
+        <v>572</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174" t="s">
+        <v>25</v>
+      </c>
+      <c r="J174" t="s">
+        <v>26</v>
+      </c>
+      <c r="K174" t="s">
+        <v>27</v>
+      </c>
+      <c r="M174" t="s">
+        <v>28</v>
+      </c>
+      <c r="N174" t="s">
         <v>574</v>
       </c>
-      <c r="F174" t="s">
-        <v>573</v>
-      </c>
-      <c r="H174">
-        <v>0</v>
-      </c>
-      <c r="I174" t="s">
-        <v>25</v>
-      </c>
-      <c r="J174" t="s">
-        <v>26</v>
-      </c>
-      <c r="K174" t="s">
-        <v>27</v>
-      </c>
-      <c r="M174" t="s">
-        <v>28</v>
-      </c>
-      <c r="N174" t="s">
-        <v>575</v>
-      </c>
       <c r="O174" t="s">
         <v>30</v>
       </c>
       <c r="Q174" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="R174" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="S174" t="s">
         <v>31</v>
       </c>
       <c r="T174" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="U174" t="s">
         <v>72</v>
@@ -13403,46 +13797,46 @@
         <v>22</v>
       </c>
       <c r="D175" t="s">
+        <v>575</v>
+      </c>
+      <c r="E175" t="s">
         <v>576</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
+        <v>575</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175" t="s">
+        <v>25</v>
+      </c>
+      <c r="J175" t="s">
+        <v>26</v>
+      </c>
+      <c r="K175" t="s">
+        <v>27</v>
+      </c>
+      <c r="M175" t="s">
+        <v>28</v>
+      </c>
+      <c r="N175" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="F175" t="s">
-        <v>576</v>
-      </c>
-      <c r="H175">
-        <v>0</v>
-      </c>
-      <c r="I175" t="s">
-        <v>25</v>
-      </c>
-      <c r="J175" t="s">
-        <v>26</v>
-      </c>
-      <c r="K175" t="s">
-        <v>27</v>
-      </c>
-      <c r="M175" t="s">
-        <v>28</v>
-      </c>
-      <c r="N175" s="2" t="s">
+      <c r="O175" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>575</v>
+      </c>
+      <c r="R175" t="s">
+        <v>575</v>
+      </c>
+      <c r="S175" t="s">
+        <v>31</v>
+      </c>
+      <c r="T175" t="s">
         <v>578</v>
-      </c>
-      <c r="O175" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q175" t="s">
-        <v>576</v>
-      </c>
-      <c r="R175" t="s">
-        <v>576</v>
-      </c>
-      <c r="S175" t="s">
-        <v>31</v>
-      </c>
-      <c r="T175" t="s">
-        <v>579</v>
       </c>
       <c r="U175" t="s">
         <v>32</v>
@@ -13456,46 +13850,46 @@
         <v>22</v>
       </c>
       <c r="D176" t="s">
+        <v>579</v>
+      </c>
+      <c r="E176" t="s">
         <v>580</v>
       </c>
-      <c r="E176" t="s">
+      <c r="F176" t="s">
+        <v>579</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+      <c r="I176" t="s">
+        <v>25</v>
+      </c>
+      <c r="J176" t="s">
+        <v>26</v>
+      </c>
+      <c r="K176" t="s">
+        <v>27</v>
+      </c>
+      <c r="M176" t="s">
+        <v>28</v>
+      </c>
+      <c r="N176" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="F176" t="s">
-        <v>580</v>
-      </c>
-      <c r="H176">
-        <v>0</v>
-      </c>
-      <c r="I176" t="s">
-        <v>25</v>
-      </c>
-      <c r="J176" t="s">
-        <v>26</v>
-      </c>
-      <c r="K176" t="s">
-        <v>27</v>
-      </c>
-      <c r="M176" t="s">
-        <v>28</v>
-      </c>
-      <c r="N176" s="2" t="s">
-        <v>582</v>
-      </c>
       <c r="O176" t="s">
         <v>30</v>
       </c>
       <c r="Q176" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R176" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="S176" t="s">
         <v>31</v>
       </c>
       <c r="T176" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="U176" t="s">
         <v>32</v>
@@ -13509,46 +13903,46 @@
         <v>22</v>
       </c>
       <c r="D177" t="s">
+        <v>582</v>
+      </c>
+      <c r="E177" t="s">
         <v>583</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
+        <v>582</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177" t="s">
+        <v>25</v>
+      </c>
+      <c r="J177" t="s">
+        <v>26</v>
+      </c>
+      <c r="K177" t="s">
+        <v>27</v>
+      </c>
+      <c r="M177" t="s">
+        <v>28</v>
+      </c>
+      <c r="N177" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="F177" t="s">
-        <v>583</v>
-      </c>
-      <c r="H177">
-        <v>0</v>
-      </c>
-      <c r="I177" t="s">
-        <v>25</v>
-      </c>
-      <c r="J177" t="s">
-        <v>26</v>
-      </c>
-      <c r="K177" t="s">
-        <v>27</v>
-      </c>
-      <c r="M177" t="s">
-        <v>28</v>
-      </c>
-      <c r="N177" s="2" t="s">
-        <v>585</v>
-      </c>
       <c r="O177" t="s">
         <v>30</v>
       </c>
       <c r="Q177" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="R177" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="S177" t="s">
         <v>31</v>
       </c>
       <c r="T177" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="U177" t="s">
         <v>32</v>
@@ -13562,46 +13956,46 @@
         <v>22</v>
       </c>
       <c r="D178" t="s">
+        <v>585</v>
+      </c>
+      <c r="E178" t="s">
         <v>586</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
+        <v>585</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+      <c r="I178" t="s">
+        <v>25</v>
+      </c>
+      <c r="J178" t="s">
+        <v>26</v>
+      </c>
+      <c r="K178" t="s">
+        <v>27</v>
+      </c>
+      <c r="M178" t="s">
+        <v>28</v>
+      </c>
+      <c r="N178" t="s">
         <v>587</v>
       </c>
-      <c r="F178" t="s">
-        <v>586</v>
-      </c>
-      <c r="H178">
-        <v>0</v>
-      </c>
-      <c r="I178" t="s">
-        <v>25</v>
-      </c>
-      <c r="J178" t="s">
-        <v>26</v>
-      </c>
-      <c r="K178" t="s">
-        <v>27</v>
-      </c>
-      <c r="M178" t="s">
-        <v>28</v>
-      </c>
-      <c r="N178" t="s">
-        <v>588</v>
-      </c>
       <c r="O178" t="s">
         <v>30</v>
       </c>
       <c r="Q178" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="R178" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="S178" t="s">
         <v>31</v>
       </c>
       <c r="T178" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="U178" t="s">
         <v>72</v>
@@ -13615,40 +14009,40 @@
         <v>22</v>
       </c>
       <c r="D179" t="s">
+        <v>588</v>
+      </c>
+      <c r="E179" t="s">
         <v>589</v>
       </c>
-      <c r="E179" t="s">
+      <c r="F179" t="s">
+        <v>588</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179" t="s">
+        <v>25</v>
+      </c>
+      <c r="J179" t="s">
+        <v>26</v>
+      </c>
+      <c r="K179" t="s">
+        <v>27</v>
+      </c>
+      <c r="M179" t="s">
+        <v>28</v>
+      </c>
+      <c r="N179" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="F179" t="s">
-        <v>589</v>
-      </c>
-      <c r="H179">
-        <v>0</v>
-      </c>
-      <c r="I179" t="s">
-        <v>25</v>
-      </c>
-      <c r="J179" t="s">
-        <v>26</v>
-      </c>
-      <c r="K179" t="s">
-        <v>27</v>
-      </c>
-      <c r="M179" t="s">
-        <v>28</v>
-      </c>
-      <c r="N179" s="2" t="s">
-        <v>591</v>
-      </c>
       <c r="O179" t="s">
         <v>30</v>
       </c>
       <c r="Q179" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="R179" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="S179" t="s">
         <v>31</v>
@@ -13665,40 +14059,40 @@
         <v>22</v>
       </c>
       <c r="D180" t="s">
+        <v>591</v>
+      </c>
+      <c r="E180" t="s">
         <v>592</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
+        <v>591</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180" t="s">
+        <v>25</v>
+      </c>
+      <c r="J180" t="s">
+        <v>26</v>
+      </c>
+      <c r="K180" t="s">
+        <v>27</v>
+      </c>
+      <c r="M180" t="s">
+        <v>28</v>
+      </c>
+      <c r="N180" t="s">
         <v>593</v>
       </c>
-      <c r="F180" t="s">
-        <v>592</v>
-      </c>
-      <c r="H180">
-        <v>0</v>
-      </c>
-      <c r="I180" t="s">
-        <v>25</v>
-      </c>
-      <c r="J180" t="s">
-        <v>26</v>
-      </c>
-      <c r="K180" t="s">
-        <v>27</v>
-      </c>
-      <c r="M180" t="s">
-        <v>28</v>
-      </c>
-      <c r="N180" t="s">
-        <v>594</v>
-      </c>
       <c r="O180" t="s">
         <v>30</v>
       </c>
       <c r="Q180" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="R180" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="S180" t="s">
         <v>31</v>
@@ -13707,7 +14101,7 @@
         <v>48</v>
       </c>
       <c r="U180" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.3">
@@ -13718,40 +14112,40 @@
         <v>22</v>
       </c>
       <c r="D181" t="s">
+        <v>595</v>
+      </c>
+      <c r="E181" t="s">
         <v>596</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
+        <v>595</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181" t="s">
+        <v>25</v>
+      </c>
+      <c r="J181" t="s">
+        <v>26</v>
+      </c>
+      <c r="K181" t="s">
+        <v>27</v>
+      </c>
+      <c r="M181" t="s">
+        <v>28</v>
+      </c>
+      <c r="N181" t="s">
         <v>597</v>
       </c>
-      <c r="F181" t="s">
-        <v>596</v>
-      </c>
-      <c r="H181">
-        <v>0</v>
-      </c>
-      <c r="I181" t="s">
-        <v>25</v>
-      </c>
-      <c r="J181" t="s">
-        <v>26</v>
-      </c>
-      <c r="K181" t="s">
-        <v>27</v>
-      </c>
-      <c r="M181" t="s">
-        <v>28</v>
-      </c>
-      <c r="N181" t="s">
-        <v>598</v>
-      </c>
       <c r="O181" t="s">
         <v>30</v>
       </c>
       <c r="Q181" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="R181" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="S181" t="s">
         <v>31</v>
@@ -13768,40 +14162,40 @@
         <v>22</v>
       </c>
       <c r="D182" t="s">
+        <v>598</v>
+      </c>
+      <c r="E182" t="s">
         <v>599</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" t="s">
+        <v>598</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182" t="s">
+        <v>25</v>
+      </c>
+      <c r="J182" t="s">
+        <v>26</v>
+      </c>
+      <c r="K182" t="s">
+        <v>27</v>
+      </c>
+      <c r="M182" t="s">
+        <v>28</v>
+      </c>
+      <c r="N182" t="s">
         <v>600</v>
       </c>
-      <c r="F182" t="s">
-        <v>599</v>
-      </c>
-      <c r="H182">
-        <v>0</v>
-      </c>
-      <c r="I182" t="s">
-        <v>25</v>
-      </c>
-      <c r="J182" t="s">
-        <v>26</v>
-      </c>
-      <c r="K182" t="s">
-        <v>27</v>
-      </c>
-      <c r="M182" t="s">
-        <v>28</v>
-      </c>
-      <c r="N182" t="s">
-        <v>601</v>
-      </c>
       <c r="O182" t="s">
         <v>30</v>
       </c>
       <c r="Q182" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="R182" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="S182" t="s">
         <v>31</v>
@@ -13818,40 +14212,40 @@
         <v>22</v>
       </c>
       <c r="D183" t="s">
+        <v>601</v>
+      </c>
+      <c r="E183" t="s">
         <v>602</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
+        <v>601</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183" t="s">
+        <v>25</v>
+      </c>
+      <c r="J183" t="s">
+        <v>26</v>
+      </c>
+      <c r="K183" t="s">
+        <v>27</v>
+      </c>
+      <c r="M183" t="s">
+        <v>28</v>
+      </c>
+      <c r="N183" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="F183" t="s">
-        <v>602</v>
-      </c>
-      <c r="H183">
-        <v>0</v>
-      </c>
-      <c r="I183" t="s">
-        <v>25</v>
-      </c>
-      <c r="J183" t="s">
-        <v>26</v>
-      </c>
-      <c r="K183" t="s">
-        <v>27</v>
-      </c>
-      <c r="M183" t="s">
-        <v>28</v>
-      </c>
-      <c r="N183" s="2" t="s">
-        <v>604</v>
-      </c>
       <c r="O183" t="s">
         <v>30</v>
       </c>
       <c r="Q183" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="R183" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="S183" t="s">
         <v>31</v>
@@ -13868,40 +14262,40 @@
         <v>22</v>
       </c>
       <c r="D184" t="s">
+        <v>604</v>
+      </c>
+      <c r="E184" t="s">
         <v>605</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
+        <v>604</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184" t="s">
+        <v>25</v>
+      </c>
+      <c r="J184" t="s">
+        <v>26</v>
+      </c>
+      <c r="K184" t="s">
+        <v>27</v>
+      </c>
+      <c r="M184" t="s">
+        <v>28</v>
+      </c>
+      <c r="N184" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="F184" t="s">
-        <v>605</v>
-      </c>
-      <c r="H184">
-        <v>0</v>
-      </c>
-      <c r="I184" t="s">
-        <v>25</v>
-      </c>
-      <c r="J184" t="s">
-        <v>26</v>
-      </c>
-      <c r="K184" t="s">
-        <v>27</v>
-      </c>
-      <c r="M184" t="s">
-        <v>28</v>
-      </c>
-      <c r="N184" s="2" t="s">
-        <v>607</v>
-      </c>
       <c r="O184" t="s">
         <v>30</v>
       </c>
       <c r="Q184" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="R184" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="S184" t="s">
         <v>31</v>
@@ -13918,40 +14312,40 @@
         <v>22</v>
       </c>
       <c r="D185" t="s">
+        <v>607</v>
+      </c>
+      <c r="E185" t="s">
         <v>608</v>
       </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
+        <v>607</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185" t="s">
+        <v>25</v>
+      </c>
+      <c r="J185" t="s">
+        <v>26</v>
+      </c>
+      <c r="K185" t="s">
+        <v>27</v>
+      </c>
+      <c r="M185" t="s">
+        <v>28</v>
+      </c>
+      <c r="N185" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="F185" t="s">
-        <v>608</v>
-      </c>
-      <c r="H185">
-        <v>0</v>
-      </c>
-      <c r="I185" t="s">
-        <v>25</v>
-      </c>
-      <c r="J185" t="s">
-        <v>26</v>
-      </c>
-      <c r="K185" t="s">
-        <v>27</v>
-      </c>
-      <c r="M185" t="s">
-        <v>28</v>
-      </c>
-      <c r="N185" s="2" t="s">
-        <v>610</v>
-      </c>
       <c r="O185" t="s">
         <v>30</v>
       </c>
       <c r="Q185" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="R185" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="S185" t="s">
         <v>31</v>
@@ -13968,40 +14362,40 @@
         <v>22</v>
       </c>
       <c r="D186" t="s">
+        <v>610</v>
+      </c>
+      <c r="E186" t="s">
         <v>611</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
+        <v>610</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186" t="s">
+        <v>25</v>
+      </c>
+      <c r="J186" t="s">
+        <v>26</v>
+      </c>
+      <c r="K186" t="s">
+        <v>27</v>
+      </c>
+      <c r="M186" t="s">
+        <v>28</v>
+      </c>
+      <c r="N186" t="s">
         <v>612</v>
       </c>
-      <c r="F186" t="s">
-        <v>611</v>
-      </c>
-      <c r="H186">
-        <v>0</v>
-      </c>
-      <c r="I186" t="s">
-        <v>25</v>
-      </c>
-      <c r="J186" t="s">
-        <v>26</v>
-      </c>
-      <c r="K186" t="s">
-        <v>27</v>
-      </c>
-      <c r="M186" t="s">
-        <v>28</v>
-      </c>
-      <c r="N186" t="s">
-        <v>613</v>
-      </c>
       <c r="O186" t="s">
         <v>30</v>
       </c>
       <c r="Q186" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="R186" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="S186" t="s">
         <v>31</v>
@@ -14021,46 +14415,46 @@
         <v>22</v>
       </c>
       <c r="D187" t="s">
+        <v>613</v>
+      </c>
+      <c r="E187" t="s">
         <v>614</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
+        <v>613</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187" t="s">
+        <v>25</v>
+      </c>
+      <c r="J187" t="s">
+        <v>26</v>
+      </c>
+      <c r="K187" t="s">
+        <v>27</v>
+      </c>
+      <c r="M187" t="s">
+        <v>28</v>
+      </c>
+      <c r="N187" t="s">
         <v>615</v>
       </c>
-      <c r="F187" t="s">
-        <v>614</v>
-      </c>
-      <c r="H187">
-        <v>0</v>
-      </c>
-      <c r="I187" t="s">
-        <v>25</v>
-      </c>
-      <c r="J187" t="s">
-        <v>26</v>
-      </c>
-      <c r="K187" t="s">
-        <v>27</v>
-      </c>
-      <c r="M187" t="s">
-        <v>28</v>
-      </c>
-      <c r="N187" t="s">
+      <c r="O187" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>613</v>
+      </c>
+      <c r="R187" t="s">
+        <v>613</v>
+      </c>
+      <c r="S187" t="s">
+        <v>31</v>
+      </c>
+      <c r="T187" t="s">
         <v>616</v>
-      </c>
-      <c r="O187" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q187" t="s">
-        <v>614</v>
-      </c>
-      <c r="R187" t="s">
-        <v>614</v>
-      </c>
-      <c r="S187" t="s">
-        <v>31</v>
-      </c>
-      <c r="T187" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.3">
@@ -14071,46 +14465,46 @@
         <v>22</v>
       </c>
       <c r="D188" t="s">
+        <v>617</v>
+      </c>
+      <c r="E188" t="s">
         <v>618</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
+        <v>617</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188" t="s">
+        <v>25</v>
+      </c>
+      <c r="J188" t="s">
+        <v>26</v>
+      </c>
+      <c r="K188" t="s">
+        <v>27</v>
+      </c>
+      <c r="M188" t="s">
+        <v>28</v>
+      </c>
+      <c r="N188" t="s">
         <v>619</v>
       </c>
-      <c r="F188" t="s">
-        <v>618</v>
-      </c>
-      <c r="H188">
-        <v>0</v>
-      </c>
-      <c r="I188" t="s">
-        <v>25</v>
-      </c>
-      <c r="J188" t="s">
-        <v>26</v>
-      </c>
-      <c r="K188" t="s">
-        <v>27</v>
-      </c>
-      <c r="M188" t="s">
-        <v>28</v>
-      </c>
-      <c r="N188" t="s">
-        <v>620</v>
-      </c>
       <c r="O188" t="s">
         <v>30</v>
       </c>
       <c r="Q188" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="R188" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="S188" t="s">
         <v>31</v>
       </c>
       <c r="T188" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.3">
@@ -14121,46 +14515,46 @@
         <v>22</v>
       </c>
       <c r="D189" t="s">
+        <v>620</v>
+      </c>
+      <c r="E189" t="s">
         <v>621</v>
       </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
+        <v>620</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189" t="s">
+        <v>25</v>
+      </c>
+      <c r="J189" t="s">
+        <v>26</v>
+      </c>
+      <c r="K189" t="s">
+        <v>27</v>
+      </c>
+      <c r="M189" t="s">
+        <v>28</v>
+      </c>
+      <c r="N189" t="s">
         <v>622</v>
       </c>
-      <c r="F189" t="s">
-        <v>621</v>
-      </c>
-      <c r="H189">
-        <v>0</v>
-      </c>
-      <c r="I189" t="s">
-        <v>25</v>
-      </c>
-      <c r="J189" t="s">
-        <v>26</v>
-      </c>
-      <c r="K189" t="s">
-        <v>27</v>
-      </c>
-      <c r="M189" t="s">
-        <v>28</v>
-      </c>
-      <c r="N189" t="s">
-        <v>623</v>
-      </c>
       <c r="O189" t="s">
         <v>30</v>
       </c>
       <c r="Q189" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="R189" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="S189" t="s">
         <v>31</v>
       </c>
       <c r="T189" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.3">
@@ -14171,46 +14565,46 @@
         <v>22</v>
       </c>
       <c r="D190" t="s">
+        <v>623</v>
+      </c>
+      <c r="E190" t="s">
         <v>624</v>
       </c>
-      <c r="E190" t="s">
+      <c r="F190" t="s">
+        <v>623</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190" t="s">
+        <v>25</v>
+      </c>
+      <c r="J190" t="s">
+        <v>26</v>
+      </c>
+      <c r="K190" t="s">
+        <v>27</v>
+      </c>
+      <c r="M190" t="s">
+        <v>28</v>
+      </c>
+      <c r="N190" t="s">
         <v>625</v>
       </c>
-      <c r="F190" t="s">
-        <v>624</v>
-      </c>
-      <c r="H190">
-        <v>0</v>
-      </c>
-      <c r="I190" t="s">
-        <v>25</v>
-      </c>
-      <c r="J190" t="s">
-        <v>26</v>
-      </c>
-      <c r="K190" t="s">
-        <v>27</v>
-      </c>
-      <c r="M190" t="s">
-        <v>28</v>
-      </c>
-      <c r="N190" t="s">
-        <v>626</v>
-      </c>
       <c r="O190" t="s">
         <v>30</v>
       </c>
       <c r="Q190" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="R190" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="S190" t="s">
         <v>31</v>
       </c>
       <c r="T190" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.3">
@@ -14221,46 +14615,46 @@
         <v>22</v>
       </c>
       <c r="D191" t="s">
+        <v>626</v>
+      </c>
+      <c r="E191" t="s">
         <v>627</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
+        <v>626</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+      <c r="I191" t="s">
+        <v>25</v>
+      </c>
+      <c r="J191" t="s">
+        <v>26</v>
+      </c>
+      <c r="K191" t="s">
+        <v>27</v>
+      </c>
+      <c r="M191" t="s">
+        <v>28</v>
+      </c>
+      <c r="N191" t="s">
         <v>628</v>
       </c>
-      <c r="F191" t="s">
-        <v>627</v>
-      </c>
-      <c r="H191">
-        <v>0</v>
-      </c>
-      <c r="I191" t="s">
-        <v>25</v>
-      </c>
-      <c r="J191" t="s">
-        <v>26</v>
-      </c>
-      <c r="K191" t="s">
-        <v>27</v>
-      </c>
-      <c r="M191" t="s">
-        <v>28</v>
-      </c>
-      <c r="N191" t="s">
-        <v>629</v>
-      </c>
       <c r="O191" t="s">
         <v>30</v>
       </c>
       <c r="Q191" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="R191" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="S191" t="s">
         <v>31</v>
       </c>
       <c r="T191" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="192" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -14271,46 +14665,46 @@
         <v>22</v>
       </c>
       <c r="D192" t="s">
+        <v>629</v>
+      </c>
+      <c r="E192" t="s">
         <v>630</v>
       </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
+        <v>629</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192" t="s">
+        <v>25</v>
+      </c>
+      <c r="J192" t="s">
+        <v>26</v>
+      </c>
+      <c r="K192" t="s">
+        <v>27</v>
+      </c>
+      <c r="M192" t="s">
+        <v>28</v>
+      </c>
+      <c r="N192" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="F192" t="s">
-        <v>630</v>
-      </c>
-      <c r="H192">
-        <v>0</v>
-      </c>
-      <c r="I192" t="s">
-        <v>25</v>
-      </c>
-      <c r="J192" t="s">
-        <v>26</v>
-      </c>
-      <c r="K192" t="s">
-        <v>27</v>
-      </c>
-      <c r="M192" t="s">
-        <v>28</v>
-      </c>
-      <c r="N192" s="2" t="s">
-        <v>632</v>
-      </c>
       <c r="O192" t="s">
         <v>30</v>
       </c>
       <c r="Q192" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="R192" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="S192" t="s">
         <v>31</v>
       </c>
       <c r="T192" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="193" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -14321,46 +14715,46 @@
         <v>22</v>
       </c>
       <c r="D193" t="s">
+        <v>632</v>
+      </c>
+      <c r="E193" t="s">
         <v>633</v>
       </c>
-      <c r="E193" t="s">
+      <c r="F193" t="s">
+        <v>632</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+      <c r="I193" t="s">
+        <v>25</v>
+      </c>
+      <c r="J193" t="s">
+        <v>26</v>
+      </c>
+      <c r="K193" t="s">
+        <v>27</v>
+      </c>
+      <c r="M193" t="s">
+        <v>28</v>
+      </c>
+      <c r="N193" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="F193" t="s">
-        <v>633</v>
-      </c>
-      <c r="H193">
-        <v>0</v>
-      </c>
-      <c r="I193" t="s">
-        <v>25</v>
-      </c>
-      <c r="J193" t="s">
-        <v>26</v>
-      </c>
-      <c r="K193" t="s">
-        <v>27</v>
-      </c>
-      <c r="M193" t="s">
-        <v>28</v>
-      </c>
-      <c r="N193" s="2" t="s">
-        <v>635</v>
-      </c>
       <c r="O193" t="s">
         <v>30</v>
       </c>
       <c r="Q193" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R193" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="S193" t="s">
         <v>31</v>
       </c>
       <c r="T193" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="194" spans="1:21" ht="172.8" x14ac:dyDescent="0.3">
@@ -14371,46 +14765,46 @@
         <v>22</v>
       </c>
       <c r="D194" t="s">
+        <v>635</v>
+      </c>
+      <c r="E194" t="s">
         <v>636</v>
       </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
+        <v>635</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194" t="s">
+        <v>25</v>
+      </c>
+      <c r="J194" t="s">
+        <v>26</v>
+      </c>
+      <c r="K194" t="s">
+        <v>27</v>
+      </c>
+      <c r="M194" t="s">
+        <v>28</v>
+      </c>
+      <c r="N194" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="F194" t="s">
-        <v>636</v>
-      </c>
-      <c r="H194">
-        <v>0</v>
-      </c>
-      <c r="I194" t="s">
-        <v>25</v>
-      </c>
-      <c r="J194" t="s">
-        <v>26</v>
-      </c>
-      <c r="K194" t="s">
-        <v>27</v>
-      </c>
-      <c r="M194" t="s">
-        <v>28</v>
-      </c>
-      <c r="N194" s="2" t="s">
-        <v>638</v>
-      </c>
       <c r="O194" t="s">
         <v>30</v>
       </c>
       <c r="Q194" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="R194" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="S194" t="s">
         <v>31</v>
       </c>
       <c r="T194" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="195" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -14421,46 +14815,46 @@
         <v>22</v>
       </c>
       <c r="D195" t="s">
+        <v>638</v>
+      </c>
+      <c r="E195" t="s">
         <v>639</v>
       </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
+        <v>638</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195" t="s">
+        <v>25</v>
+      </c>
+      <c r="J195" t="s">
+        <v>26</v>
+      </c>
+      <c r="K195" t="s">
+        <v>27</v>
+      </c>
+      <c r="M195" t="s">
+        <v>28</v>
+      </c>
+      <c r="N195" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="F195" t="s">
-        <v>639</v>
-      </c>
-      <c r="H195">
-        <v>0</v>
-      </c>
-      <c r="I195" t="s">
-        <v>25</v>
-      </c>
-      <c r="J195" t="s">
-        <v>26</v>
-      </c>
-      <c r="K195" t="s">
-        <v>27</v>
-      </c>
-      <c r="M195" t="s">
-        <v>28</v>
-      </c>
-      <c r="N195" s="2" t="s">
-        <v>641</v>
-      </c>
       <c r="O195" t="s">
         <v>30</v>
       </c>
       <c r="Q195" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="R195" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="S195" t="s">
         <v>31</v>
       </c>
       <c r="T195" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="196" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
@@ -14471,46 +14865,46 @@
         <v>22</v>
       </c>
       <c r="D196" t="s">
+        <v>641</v>
+      </c>
+      <c r="E196" t="s">
         <v>642</v>
       </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
+        <v>641</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196" t="s">
+        <v>25</v>
+      </c>
+      <c r="J196" t="s">
+        <v>26</v>
+      </c>
+      <c r="K196" t="s">
+        <v>27</v>
+      </c>
+      <c r="M196" t="s">
+        <v>28</v>
+      </c>
+      <c r="N196" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="F196" t="s">
-        <v>642</v>
-      </c>
-      <c r="H196">
-        <v>0</v>
-      </c>
-      <c r="I196" t="s">
-        <v>25</v>
-      </c>
-      <c r="J196" t="s">
-        <v>26</v>
-      </c>
-      <c r="K196" t="s">
-        <v>27</v>
-      </c>
-      <c r="M196" t="s">
-        <v>28</v>
-      </c>
-      <c r="N196" s="2" t="s">
-        <v>644</v>
-      </c>
       <c r="O196" t="s">
         <v>30</v>
       </c>
       <c r="Q196" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="R196" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S196" t="s">
         <v>31</v>
       </c>
       <c r="T196" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.3">
@@ -14521,46 +14915,46 @@
         <v>22</v>
       </c>
       <c r="D197" t="s">
+        <v>644</v>
+      </c>
+      <c r="E197" t="s">
         <v>645</v>
       </c>
-      <c r="E197" t="s">
+      <c r="F197" t="s">
+        <v>644</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197" t="s">
+        <v>25</v>
+      </c>
+      <c r="J197" t="s">
+        <v>26</v>
+      </c>
+      <c r="K197" t="s">
+        <v>27</v>
+      </c>
+      <c r="M197" t="s">
+        <v>28</v>
+      </c>
+      <c r="N197" t="s">
         <v>646</v>
       </c>
-      <c r="F197" t="s">
-        <v>645</v>
-      </c>
-      <c r="H197">
-        <v>0</v>
-      </c>
-      <c r="I197" t="s">
-        <v>25</v>
-      </c>
-      <c r="J197" t="s">
-        <v>26</v>
-      </c>
-      <c r="K197" t="s">
-        <v>27</v>
-      </c>
-      <c r="M197" t="s">
-        <v>28</v>
-      </c>
-      <c r="N197" t="s">
-        <v>647</v>
-      </c>
       <c r="O197" t="s">
         <v>30</v>
       </c>
       <c r="Q197" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="R197" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="S197" t="s">
         <v>31</v>
       </c>
       <c r="T197" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.3">
@@ -14571,46 +14965,46 @@
         <v>22</v>
       </c>
       <c r="D198" t="s">
+        <v>647</v>
+      </c>
+      <c r="E198" t="s">
         <v>648</v>
       </c>
-      <c r="E198" t="s">
+      <c r="F198" t="s">
+        <v>647</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198" t="s">
+        <v>25</v>
+      </c>
+      <c r="J198" t="s">
+        <v>26</v>
+      </c>
+      <c r="K198" t="s">
+        <v>27</v>
+      </c>
+      <c r="M198" t="s">
+        <v>28</v>
+      </c>
+      <c r="N198" t="s">
         <v>649</v>
       </c>
-      <c r="F198" t="s">
-        <v>648</v>
-      </c>
-      <c r="H198">
-        <v>0</v>
-      </c>
-      <c r="I198" t="s">
-        <v>25</v>
-      </c>
-      <c r="J198" t="s">
-        <v>26</v>
-      </c>
-      <c r="K198" t="s">
-        <v>27</v>
-      </c>
-      <c r="M198" t="s">
-        <v>28</v>
-      </c>
-      <c r="N198" t="s">
-        <v>650</v>
-      </c>
       <c r="O198" t="s">
         <v>30</v>
       </c>
       <c r="Q198" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="R198" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="S198" t="s">
         <v>31</v>
       </c>
       <c r="T198" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="199" spans="1:21" ht="115.2" x14ac:dyDescent="0.3">
@@ -14621,46 +15015,46 @@
         <v>22</v>
       </c>
       <c r="D199" t="s">
+        <v>650</v>
+      </c>
+      <c r="E199" t="s">
         <v>651</v>
       </c>
-      <c r="E199" t="s">
+      <c r="F199" t="s">
+        <v>650</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199" t="s">
+        <v>25</v>
+      </c>
+      <c r="J199" t="s">
+        <v>26</v>
+      </c>
+      <c r="K199" t="s">
+        <v>27</v>
+      </c>
+      <c r="M199" t="s">
+        <v>28</v>
+      </c>
+      <c r="N199" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="F199" t="s">
-        <v>651</v>
-      </c>
-      <c r="H199">
-        <v>0</v>
-      </c>
-      <c r="I199" t="s">
-        <v>25</v>
-      </c>
-      <c r="J199" t="s">
-        <v>26</v>
-      </c>
-      <c r="K199" t="s">
-        <v>27</v>
-      </c>
-      <c r="M199" t="s">
-        <v>28</v>
-      </c>
-      <c r="N199" s="2" t="s">
-        <v>653</v>
-      </c>
       <c r="O199" t="s">
         <v>30</v>
       </c>
       <c r="Q199" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R199" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="S199" t="s">
         <v>31</v>
       </c>
       <c r="T199" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.3">
@@ -14671,46 +15065,46 @@
         <v>22</v>
       </c>
       <c r="D200" t="s">
+        <v>653</v>
+      </c>
+      <c r="E200" t="s">
         <v>654</v>
       </c>
-      <c r="E200" t="s">
+      <c r="F200" t="s">
+        <v>653</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200" t="s">
+        <v>25</v>
+      </c>
+      <c r="J200" t="s">
+        <v>26</v>
+      </c>
+      <c r="K200" t="s">
+        <v>27</v>
+      </c>
+      <c r="M200" t="s">
+        <v>28</v>
+      </c>
+      <c r="N200" t="s">
         <v>655</v>
       </c>
-      <c r="F200" t="s">
-        <v>654</v>
-      </c>
-      <c r="H200">
-        <v>0</v>
-      </c>
-      <c r="I200" t="s">
-        <v>25</v>
-      </c>
-      <c r="J200" t="s">
-        <v>26</v>
-      </c>
-      <c r="K200" t="s">
-        <v>27</v>
-      </c>
-      <c r="M200" t="s">
-        <v>28</v>
-      </c>
-      <c r="N200" t="s">
-        <v>656</v>
-      </c>
       <c r="O200" t="s">
         <v>30</v>
       </c>
       <c r="Q200" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="R200" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="S200" t="s">
         <v>31</v>
       </c>
       <c r="T200" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.3">
@@ -14721,46 +15115,46 @@
         <v>22</v>
       </c>
       <c r="D201" t="s">
+        <v>656</v>
+      </c>
+      <c r="E201" t="s">
         <v>657</v>
       </c>
-      <c r="E201" t="s">
+      <c r="F201" t="s">
+        <v>656</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201" t="s">
+        <v>25</v>
+      </c>
+      <c r="J201" t="s">
+        <v>26</v>
+      </c>
+      <c r="K201" t="s">
+        <v>27</v>
+      </c>
+      <c r="M201" t="s">
+        <v>28</v>
+      </c>
+      <c r="N201" t="s">
         <v>658</v>
       </c>
-      <c r="F201" t="s">
-        <v>657</v>
-      </c>
-      <c r="H201">
-        <v>0</v>
-      </c>
-      <c r="I201" t="s">
-        <v>25</v>
-      </c>
-      <c r="J201" t="s">
-        <v>26</v>
-      </c>
-      <c r="K201" t="s">
-        <v>27</v>
-      </c>
-      <c r="M201" t="s">
-        <v>28</v>
-      </c>
-      <c r="N201" t="s">
-        <v>659</v>
-      </c>
       <c r="O201" t="s">
         <v>30</v>
       </c>
       <c r="Q201" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="R201" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="S201" t="s">
         <v>31</v>
       </c>
       <c r="T201" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="202" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
@@ -14771,40 +15165,40 @@
         <v>22</v>
       </c>
       <c r="D202" t="s">
+        <v>659</v>
+      </c>
+      <c r="E202" t="s">
         <v>660</v>
       </c>
-      <c r="E202" t="s">
+      <c r="F202" t="s">
+        <v>659</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202" t="s">
+        <v>25</v>
+      </c>
+      <c r="J202" t="s">
+        <v>26</v>
+      </c>
+      <c r="K202" t="s">
+        <v>27</v>
+      </c>
+      <c r="M202" t="s">
+        <v>28</v>
+      </c>
+      <c r="N202" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="F202" t="s">
-        <v>660</v>
-      </c>
-      <c r="H202">
-        <v>0</v>
-      </c>
-      <c r="I202" t="s">
-        <v>25</v>
-      </c>
-      <c r="J202" t="s">
-        <v>26</v>
-      </c>
-      <c r="K202" t="s">
-        <v>27</v>
-      </c>
-      <c r="M202" t="s">
-        <v>28</v>
-      </c>
-      <c r="N202" s="2" t="s">
-        <v>662</v>
-      </c>
       <c r="O202" t="s">
         <v>30</v>
       </c>
       <c r="Q202" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="R202" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="S202" t="s">
         <v>31</v>
@@ -14816,7 +15210,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="203" spans="1:21" ht="144" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>21</v>
       </c>
@@ -14824,247 +15218,1295 @@
         <v>22</v>
       </c>
       <c r="D203" t="s">
+        <v>662</v>
+      </c>
+      <c r="E203" t="s">
         <v>663</v>
       </c>
-      <c r="E203" t="s">
+      <c r="F203" t="s">
+        <v>662</v>
+      </c>
+      <c r="H203">
+        <v>0</v>
+      </c>
+      <c r="I203" t="s">
+        <v>25</v>
+      </c>
+      <c r="J203" t="s">
+        <v>26</v>
+      </c>
+      <c r="K203" t="s">
+        <v>27</v>
+      </c>
+      <c r="M203" t="s">
+        <v>28</v>
+      </c>
+      <c r="N203" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F203" t="s">
-        <v>663</v>
-      </c>
-      <c r="H203">
-        <v>0</v>
-      </c>
-      <c r="I203" t="s">
-        <v>25</v>
-      </c>
-      <c r="J203" t="s">
-        <v>26</v>
-      </c>
-      <c r="K203" t="s">
-        <v>27</v>
-      </c>
-      <c r="M203" t="s">
-        <v>28</v>
-      </c>
-      <c r="N203" s="2" t="s">
+      <c r="O203" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>662</v>
+      </c>
+      <c r="R203" t="s">
+        <v>662</v>
+      </c>
+      <c r="S203" t="s">
+        <v>31</v>
+      </c>
+      <c r="T203" t="s">
         <v>665</v>
       </c>
-      <c r="O203" t="s">
+      <c r="U203" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="204" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>21</v>
+      </c>
+      <c r="C204" t="s">
+        <v>22</v>
+      </c>
+      <c r="D204" t="s">
         <v>666</v>
       </c>
-      <c r="Q203" t="s">
-        <v>663</v>
-      </c>
-      <c r="R203" t="s">
-        <v>663</v>
-      </c>
-      <c r="S203" t="s">
+      <c r="E204" t="s">
         <v>667</v>
       </c>
-      <c r="T203" t="s">
+      <c r="F204" t="s">
+        <v>666</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204" t="s">
+        <v>25</v>
+      </c>
+      <c r="J204" t="s">
+        <v>26</v>
+      </c>
+      <c r="K204" t="s">
+        <v>27</v>
+      </c>
+      <c r="M204" t="s">
+        <v>28</v>
+      </c>
+      <c r="N204" s="2" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="204" spans="1:21" ht="144" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>21</v>
-      </c>
-      <c r="C204" t="s">
-        <v>22</v>
-      </c>
-      <c r="D204" t="s">
+      <c r="O204" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>666</v>
+      </c>
+      <c r="R204" t="s">
+        <v>666</v>
+      </c>
+      <c r="S204" t="s">
+        <v>31</v>
+      </c>
+      <c r="T204" t="s">
+        <v>665</v>
+      </c>
+      <c r="U204" t="s">
         <v>669</v>
       </c>
-      <c r="E204" t="s">
+    </row>
+    <row r="205" spans="1:21" ht="216" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>21</v>
+      </c>
+      <c r="C205" t="s">
+        <v>22</v>
+      </c>
+      <c r="D205" t="s">
         <v>670</v>
       </c>
-      <c r="F204" t="s">
-        <v>669</v>
-      </c>
-      <c r="H204">
-        <v>0</v>
-      </c>
-      <c r="I204" t="s">
-        <v>25</v>
-      </c>
-      <c r="J204" t="s">
-        <v>26</v>
-      </c>
-      <c r="K204" t="s">
-        <v>27</v>
-      </c>
-      <c r="M204" t="s">
-        <v>28</v>
-      </c>
-      <c r="N204" s="2" t="s">
+      <c r="E205" t="s">
         <v>671</v>
       </c>
-      <c r="O204" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q204" t="s">
-        <v>669</v>
-      </c>
-      <c r="R204" t="s">
-        <v>669</v>
-      </c>
-      <c r="S204" t="s">
+      <c r="F205" t="s">
+        <v>670</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205" t="s">
+        <v>25</v>
+      </c>
+      <c r="J205" t="s">
+        <v>26</v>
+      </c>
+      <c r="K205" t="s">
+        <v>27</v>
+      </c>
+      <c r="M205" t="s">
+        <v>28</v>
+      </c>
+      <c r="N205" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="T204" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="205" spans="1:21" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>21</v>
-      </c>
-      <c r="C205" t="s">
-        <v>22</v>
-      </c>
-      <c r="D205" t="s">
+      <c r="O205" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>670</v>
+      </c>
+      <c r="R205" t="s">
+        <v>670</v>
+      </c>
+      <c r="S205" t="s">
+        <v>31</v>
+      </c>
+      <c r="T205" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="206" spans="1:21" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>21</v>
+      </c>
+      <c r="C206" t="s">
+        <v>22</v>
+      </c>
+      <c r="D206" t="s">
         <v>673</v>
       </c>
-      <c r="E205" t="s">
+      <c r="E206" t="s">
         <v>674</v>
       </c>
-      <c r="F205" t="s">
+      <c r="F206" t="s">
         <v>673</v>
       </c>
-      <c r="H205">
-        <v>0</v>
-      </c>
-      <c r="I205" t="s">
-        <v>25</v>
-      </c>
-      <c r="J205" t="s">
-        <v>26</v>
-      </c>
-      <c r="K205" t="s">
-        <v>27</v>
-      </c>
-      <c r="M205" t="s">
-        <v>28</v>
-      </c>
-      <c r="N205" s="2" t="s">
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206" t="s">
+        <v>25</v>
+      </c>
+      <c r="J206" t="s">
+        <v>26</v>
+      </c>
+      <c r="K206" t="s">
+        <v>27</v>
+      </c>
+      <c r="M206" t="s">
+        <v>28</v>
+      </c>
+      <c r="N206" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="O205" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q205" t="s">
+      <c r="O206" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q206" t="s">
         <v>673</v>
       </c>
-      <c r="R205" t="s">
+      <c r="R206" t="s">
         <v>673</v>
       </c>
-      <c r="S205" t="s">
+      <c r="S206" t="s">
+        <v>31</v>
+      </c>
+      <c r="T206" t="s">
         <v>676</v>
       </c>
-      <c r="T205" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="206" spans="1:21" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>21</v>
-      </c>
-      <c r="C206" t="s">
-        <v>22</v>
-      </c>
-      <c r="D206" t="s">
+      <c r="U206" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="207" spans="1:21" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>21</v>
+      </c>
+      <c r="C207" t="s">
+        <v>22</v>
+      </c>
+      <c r="D207" t="s">
         <v>677</v>
       </c>
-      <c r="E206" t="s">
+      <c r="E207" t="s">
         <v>678</v>
       </c>
-      <c r="F206" t="s">
+      <c r="F207" t="s">
         <v>677</v>
       </c>
-      <c r="H206">
-        <v>0</v>
-      </c>
-      <c r="I206" t="s">
-        <v>25</v>
-      </c>
-      <c r="J206" t="s">
-        <v>26</v>
-      </c>
-      <c r="K206" t="s">
-        <v>27</v>
-      </c>
-      <c r="M206" t="s">
-        <v>28</v>
-      </c>
-      <c r="N206" s="2" t="s">
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207" t="s">
+        <v>25</v>
+      </c>
+      <c r="J207" t="s">
+        <v>26</v>
+      </c>
+      <c r="K207" t="s">
+        <v>27</v>
+      </c>
+      <c r="M207" t="s">
+        <v>28</v>
+      </c>
+      <c r="N207" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="O206" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q206" t="s">
+      <c r="O207" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q207" t="s">
         <v>677</v>
       </c>
-      <c r="R206" t="s">
+      <c r="R207" t="s">
         <v>677</v>
       </c>
-      <c r="S206" t="s">
+      <c r="S207" t="s">
+        <v>31</v>
+      </c>
+      <c r="T207" t="s">
         <v>676</v>
       </c>
-      <c r="T206" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>21</v>
-      </c>
-      <c r="C207" t="s">
-        <v>22</v>
-      </c>
-      <c r="D207" t="s">
+      <c r="U207" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="208" spans="1:21" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>21</v>
+      </c>
+      <c r="C208" t="s">
+        <v>22</v>
+      </c>
+      <c r="D208" t="s">
         <v>680</v>
       </c>
-      <c r="E207" t="s">
+      <c r="E208" t="s">
         <v>681</v>
       </c>
-      <c r="F207" t="s">
+      <c r="F208" t="s">
         <v>680</v>
       </c>
-      <c r="H207">
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="I208" t="s">
+        <v>25</v>
+      </c>
+      <c r="J208" t="s">
+        <v>26</v>
+      </c>
+      <c r="K208" t="s">
+        <v>27</v>
+      </c>
+      <c r="M208" t="s">
+        <v>28</v>
+      </c>
+      <c r="N208" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="O208" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>680</v>
+      </c>
+      <c r="R208" t="s">
+        <v>680</v>
+      </c>
+      <c r="S208" t="s">
+        <v>31</v>
+      </c>
+      <c r="T208" t="s">
+        <v>676</v>
+      </c>
+      <c r="U208" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="209" spans="1:21" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>21</v>
+      </c>
+      <c r="C209" t="s">
+        <v>22</v>
+      </c>
+      <c r="D209" t="s">
+        <v>683</v>
+      </c>
+      <c r="E209" t="s">
+        <v>684</v>
+      </c>
+      <c r="F209" t="s">
+        <v>683</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209" t="s">
+        <v>25</v>
+      </c>
+      <c r="J209" t="s">
+        <v>26</v>
+      </c>
+      <c r="K209" t="s">
+        <v>27</v>
+      </c>
+      <c r="M209" t="s">
+        <v>28</v>
+      </c>
+      <c r="N209" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="O209" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>683</v>
+      </c>
+      <c r="R209" t="s">
+        <v>683</v>
+      </c>
+      <c r="S209" t="s">
+        <v>31</v>
+      </c>
+      <c r="T209" t="s">
+        <v>676</v>
+      </c>
+      <c r="U209" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="210" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>21</v>
+      </c>
+      <c r="C210" t="s">
+        <v>22</v>
+      </c>
+      <c r="D210" t="s">
+        <v>686</v>
+      </c>
+      <c r="E210" t="s">
+        <v>687</v>
+      </c>
+      <c r="F210" t="s">
+        <v>686</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+      <c r="I210" t="s">
+        <v>25</v>
+      </c>
+      <c r="J210" t="s">
+        <v>26</v>
+      </c>
+      <c r="K210" t="s">
+        <v>27</v>
+      </c>
+      <c r="M210" t="s">
+        <v>28</v>
+      </c>
+      <c r="N210" t="s">
+        <v>688</v>
+      </c>
+      <c r="O210" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>686</v>
+      </c>
+      <c r="R210" t="s">
+        <v>686</v>
+      </c>
+      <c r="S210" t="s">
+        <v>31</v>
+      </c>
+      <c r="T210" t="s">
+        <v>676</v>
+      </c>
+      <c r="U210" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="211" spans="1:21" ht="72" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>21</v>
+      </c>
+      <c r="C211" t="s">
+        <v>22</v>
+      </c>
+      <c r="D211" t="s">
+        <v>689</v>
+      </c>
+      <c r="E211" t="s">
+        <v>690</v>
+      </c>
+      <c r="F211" t="s">
+        <v>689</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211" t="s">
+        <v>25</v>
+      </c>
+      <c r="J211" t="s">
+        <v>26</v>
+      </c>
+      <c r="K211" t="s">
+        <v>27</v>
+      </c>
+      <c r="M211" t="s">
+        <v>28</v>
+      </c>
+      <c r="N211" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="O211" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>689</v>
+      </c>
+      <c r="R211" t="s">
+        <v>689</v>
+      </c>
+      <c r="S211" t="s">
+        <v>31</v>
+      </c>
+      <c r="T211" t="s">
+        <v>676</v>
+      </c>
+      <c r="U211" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="212" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>21</v>
+      </c>
+      <c r="C212" t="s">
+        <v>22</v>
+      </c>
+      <c r="D212" t="s">
+        <v>693</v>
+      </c>
+      <c r="E212" t="s">
+        <v>694</v>
+      </c>
+      <c r="F212" t="s">
+        <v>693</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+      <c r="I212" t="s">
+        <v>25</v>
+      </c>
+      <c r="J212" t="s">
+        <v>26</v>
+      </c>
+      <c r="K212" t="s">
+        <v>27</v>
+      </c>
+      <c r="M212" t="s">
+        <v>28</v>
+      </c>
+      <c r="N212" t="s">
+        <v>695</v>
+      </c>
+      <c r="O212" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>693</v>
+      </c>
+      <c r="R212" t="s">
+        <v>693</v>
+      </c>
+      <c r="S212" t="s">
+        <v>31</v>
+      </c>
+      <c r="T212" t="s">
+        <v>676</v>
+      </c>
+      <c r="U212" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="213" spans="1:21" ht="72" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>21</v>
+      </c>
+      <c r="C213" t="s">
+        <v>22</v>
+      </c>
+      <c r="D213" t="s">
+        <v>696</v>
+      </c>
+      <c r="E213" t="s">
+        <v>697</v>
+      </c>
+      <c r="F213" t="s">
+        <v>696</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213" t="s">
+        <v>25</v>
+      </c>
+      <c r="J213" t="s">
+        <v>26</v>
+      </c>
+      <c r="K213" t="s">
+        <v>27</v>
+      </c>
+      <c r="M213" t="s">
+        <v>28</v>
+      </c>
+      <c r="N213" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="O213" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>696</v>
+      </c>
+      <c r="R213" t="s">
+        <v>696</v>
+      </c>
+      <c r="S213" t="s">
+        <v>31</v>
+      </c>
+      <c r="T213" t="s">
+        <v>676</v>
+      </c>
+      <c r="U213" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="214" spans="1:21" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>21</v>
+      </c>
+      <c r="C214" t="s">
+        <v>22</v>
+      </c>
+      <c r="D214" t="s">
+        <v>699</v>
+      </c>
+      <c r="E214" t="s">
+        <v>700</v>
+      </c>
+      <c r="F214" t="s">
+        <v>699</v>
+      </c>
+      <c r="H214">
+        <v>0</v>
+      </c>
+      <c r="I214" t="s">
+        <v>25</v>
+      </c>
+      <c r="J214" t="s">
+        <v>26</v>
+      </c>
+      <c r="K214" t="s">
+        <v>27</v>
+      </c>
+      <c r="M214" t="s">
+        <v>28</v>
+      </c>
+      <c r="N214" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="O214" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>699</v>
+      </c>
+      <c r="R214" t="s">
+        <v>699</v>
+      </c>
+      <c r="S214" t="s">
+        <v>31</v>
+      </c>
+      <c r="T214" t="s">
+        <v>676</v>
+      </c>
+      <c r="U214" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="215" spans="1:21" ht="216" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>21</v>
+      </c>
+      <c r="C215" t="s">
+        <v>22</v>
+      </c>
+      <c r="D215" t="s">
+        <v>702</v>
+      </c>
+      <c r="E215" t="s">
+        <v>703</v>
+      </c>
+      <c r="F215" t="s">
+        <v>702</v>
+      </c>
+      <c r="H215">
+        <v>0</v>
+      </c>
+      <c r="I215" t="s">
+        <v>25</v>
+      </c>
+      <c r="J215" t="s">
+        <v>26</v>
+      </c>
+      <c r="K215" t="s">
+        <v>27</v>
+      </c>
+      <c r="M215" t="s">
+        <v>28</v>
+      </c>
+      <c r="N215" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="O215" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>702</v>
+      </c>
+      <c r="R215" t="s">
+        <v>702</v>
+      </c>
+      <c r="S215" t="s">
+        <v>31</v>
+      </c>
+      <c r="T215" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="216" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>21</v>
+      </c>
+      <c r="C216" t="s">
+        <v>22</v>
+      </c>
+      <c r="D216" t="s">
+        <v>704</v>
+      </c>
+      <c r="E216" t="s">
+        <v>705</v>
+      </c>
+      <c r="F216" t="s">
+        <v>704</v>
+      </c>
+      <c r="H216">
+        <v>0</v>
+      </c>
+      <c r="I216" t="s">
+        <v>25</v>
+      </c>
+      <c r="J216" t="s">
+        <v>26</v>
+      </c>
+      <c r="K216" t="s">
+        <v>27</v>
+      </c>
+      <c r="M216" t="s">
+        <v>28</v>
+      </c>
+      <c r="N216" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="O216" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>704</v>
+      </c>
+      <c r="R216" t="s">
+        <v>704</v>
+      </c>
+      <c r="S216" t="s">
+        <v>31</v>
+      </c>
+      <c r="T216" t="s">
+        <v>676</v>
+      </c>
+      <c r="U216" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="217" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>21</v>
+      </c>
+      <c r="C217" t="s">
+        <v>22</v>
+      </c>
+      <c r="D217" t="s">
+        <v>706</v>
+      </c>
+      <c r="E217" t="s">
+        <v>707</v>
+      </c>
+      <c r="F217" t="s">
+        <v>706</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+      <c r="I217" t="s">
+        <v>25</v>
+      </c>
+      <c r="J217" t="s">
+        <v>26</v>
+      </c>
+      <c r="K217" t="s">
+        <v>27</v>
+      </c>
+      <c r="M217" t="s">
+        <v>28</v>
+      </c>
+      <c r="N217" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="O217" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>706</v>
+      </c>
+      <c r="R217" t="s">
+        <v>706</v>
+      </c>
+      <c r="S217" t="s">
+        <v>31</v>
+      </c>
+      <c r="T217" t="s">
+        <v>676</v>
+      </c>
+      <c r="U217" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="218" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>21</v>
+      </c>
+      <c r="C218" t="s">
+        <v>22</v>
+      </c>
+      <c r="D218" t="s">
+        <v>708</v>
+      </c>
+      <c r="E218" t="s">
+        <v>709</v>
+      </c>
+      <c r="F218" t="s">
+        <v>708</v>
+      </c>
+      <c r="H218">
+        <v>0</v>
+      </c>
+      <c r="I218" t="s">
+        <v>25</v>
+      </c>
+      <c r="J218" t="s">
+        <v>26</v>
+      </c>
+      <c r="K218" t="s">
+        <v>27</v>
+      </c>
+      <c r="M218" t="s">
+        <v>28</v>
+      </c>
+      <c r="N218" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="O218" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>708</v>
+      </c>
+      <c r="R218" t="s">
+        <v>708</v>
+      </c>
+      <c r="S218" t="s">
+        <v>31</v>
+      </c>
+      <c r="T218" t="s">
+        <v>711</v>
+      </c>
+      <c r="U218" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="219" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>21</v>
+      </c>
+      <c r="C219" t="s">
+        <v>22</v>
+      </c>
+      <c r="D219" t="s">
+        <v>713</v>
+      </c>
+      <c r="E219" t="s">
+        <v>714</v>
+      </c>
+      <c r="F219" t="s">
+        <v>713</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219" t="s">
+        <v>25</v>
+      </c>
+      <c r="J219" t="s">
+        <v>26</v>
+      </c>
+      <c r="K219" t="s">
+        <v>27</v>
+      </c>
+      <c r="M219" t="s">
+        <v>28</v>
+      </c>
+      <c r="N219" t="s">
+        <v>715</v>
+      </c>
+      <c r="O219" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>713</v>
+      </c>
+      <c r="R219" t="s">
+        <v>713</v>
+      </c>
+      <c r="S219" t="s">
+        <v>31</v>
+      </c>
+      <c r="T219" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="220" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>21</v>
+      </c>
+      <c r="C220" t="s">
+        <v>22</v>
+      </c>
+      <c r="D220" t="s">
+        <v>716</v>
+      </c>
+      <c r="E220" t="s">
+        <v>717</v>
+      </c>
+      <c r="F220" t="s">
+        <v>716</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+      <c r="I220" t="s">
+        <v>25</v>
+      </c>
+      <c r="J220" t="s">
+        <v>26</v>
+      </c>
+      <c r="K220" t="s">
+        <v>27</v>
+      </c>
+      <c r="M220" t="s">
+        <v>28</v>
+      </c>
+      <c r="N220" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="O220" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>716</v>
+      </c>
+      <c r="R220" t="s">
+        <v>716</v>
+      </c>
+      <c r="S220" t="s">
+        <v>31</v>
+      </c>
+      <c r="T220" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="221" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>21</v>
+      </c>
+      <c r="C221" t="s">
+        <v>22</v>
+      </c>
+      <c r="D221" t="s">
+        <v>719</v>
+      </c>
+      <c r="E221" t="s">
+        <v>720</v>
+      </c>
+      <c r="F221" t="s">
+        <v>719</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221" t="s">
+        <v>25</v>
+      </c>
+      <c r="J221" t="s">
+        <v>26</v>
+      </c>
+      <c r="K221" t="s">
+        <v>27</v>
+      </c>
+      <c r="M221" t="s">
+        <v>28</v>
+      </c>
+      <c r="N221" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="O221" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>719</v>
+      </c>
+      <c r="R221" t="s">
+        <v>719</v>
+      </c>
+      <c r="S221" t="s">
+        <v>31</v>
+      </c>
+      <c r="T221" t="s">
+        <v>711</v>
+      </c>
+      <c r="U221" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="222" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>21</v>
+      </c>
+      <c r="C222" t="s">
+        <v>22</v>
+      </c>
+      <c r="D222" t="s">
+        <v>722</v>
+      </c>
+      <c r="E222" t="s">
+        <v>723</v>
+      </c>
+      <c r="F222" t="s">
+        <v>722</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222" t="s">
+        <v>25</v>
+      </c>
+      <c r="J222" t="s">
+        <v>26</v>
+      </c>
+      <c r="K222" t="s">
+        <v>27</v>
+      </c>
+      <c r="M222" t="s">
+        <v>28</v>
+      </c>
+      <c r="N222" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="O222" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>722</v>
+      </c>
+      <c r="R222" t="s">
+        <v>722</v>
+      </c>
+      <c r="S222" t="s">
+        <v>31</v>
+      </c>
+      <c r="T222" t="s">
+        <v>711</v>
+      </c>
+      <c r="U222" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="223" spans="1:21" ht="144" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>21</v>
+      </c>
+      <c r="C223" t="s">
+        <v>22</v>
+      </c>
+      <c r="D223" t="s">
+        <v>725</v>
+      </c>
+      <c r="E223" t="s">
+        <v>726</v>
+      </c>
+      <c r="F223" t="s">
+        <v>725</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223" t="s">
+        <v>25</v>
+      </c>
+      <c r="J223" t="s">
+        <v>26</v>
+      </c>
+      <c r="K223" t="s">
+        <v>27</v>
+      </c>
+      <c r="M223" t="s">
+        <v>28</v>
+      </c>
+      <c r="N223" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="O223" t="s">
+        <v>728</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>725</v>
+      </c>
+      <c r="R223" t="s">
+        <v>725</v>
+      </c>
+      <c r="S223" t="s">
+        <v>729</v>
+      </c>
+      <c r="T223" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="224" spans="1:21" ht="144" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>21</v>
+      </c>
+      <c r="C224" t="s">
+        <v>22</v>
+      </c>
+      <c r="D224" t="s">
+        <v>731</v>
+      </c>
+      <c r="E224" t="s">
+        <v>732</v>
+      </c>
+      <c r="F224" t="s">
+        <v>731</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224" t="s">
+        <v>25</v>
+      </c>
+      <c r="J224" t="s">
+        <v>26</v>
+      </c>
+      <c r="K224" t="s">
+        <v>27</v>
+      </c>
+      <c r="M224" t="s">
+        <v>28</v>
+      </c>
+      <c r="N224" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="O224" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>731</v>
+      </c>
+      <c r="R224" t="s">
+        <v>731</v>
+      </c>
+      <c r="S224" t="s">
+        <v>734</v>
+      </c>
+      <c r="T224" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="225" spans="1:20" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>21</v>
+      </c>
+      <c r="C225" t="s">
+        <v>22</v>
+      </c>
+      <c r="D225" t="s">
+        <v>735</v>
+      </c>
+      <c r="E225" t="s">
+        <v>736</v>
+      </c>
+      <c r="F225" t="s">
+        <v>735</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225" t="s">
+        <v>25</v>
+      </c>
+      <c r="J225" t="s">
+        <v>26</v>
+      </c>
+      <c r="K225" t="s">
+        <v>27</v>
+      </c>
+      <c r="M225" t="s">
+        <v>28</v>
+      </c>
+      <c r="N225" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="O225" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>735</v>
+      </c>
+      <c r="R225" t="s">
+        <v>735</v>
+      </c>
+      <c r="S225" t="s">
+        <v>738</v>
+      </c>
+      <c r="T225" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="226" spans="1:20" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>21</v>
+      </c>
+      <c r="C226" t="s">
+        <v>22</v>
+      </c>
+      <c r="D226" t="s">
+        <v>739</v>
+      </c>
+      <c r="E226" t="s">
+        <v>740</v>
+      </c>
+      <c r="F226" t="s">
+        <v>739</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+      <c r="I226" t="s">
+        <v>25</v>
+      </c>
+      <c r="J226" t="s">
+        <v>26</v>
+      </c>
+      <c r="K226" t="s">
+        <v>27</v>
+      </c>
+      <c r="M226" t="s">
+        <v>28</v>
+      </c>
+      <c r="N226" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="O226" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>739</v>
+      </c>
+      <c r="R226" t="s">
+        <v>739</v>
+      </c>
+      <c r="S226" t="s">
+        <v>738</v>
+      </c>
+      <c r="T226" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="227" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>21</v>
+      </c>
+      <c r="C227" t="s">
+        <v>22</v>
+      </c>
+      <c r="D227" t="s">
+        <v>742</v>
+      </c>
+      <c r="E227" t="s">
+        <v>743</v>
+      </c>
+      <c r="F227" t="s">
+        <v>742</v>
+      </c>
+      <c r="H227">
         <v>127</v>
       </c>
-      <c r="I207" t="s">
-        <v>25</v>
-      </c>
-      <c r="J207" t="s">
-        <v>26</v>
-      </c>
-      <c r="K207" t="s">
-        <v>27</v>
-      </c>
-      <c r="M207" t="s">
-        <v>28</v>
-      </c>
-      <c r="N207" t="s">
-        <v>682</v>
-      </c>
-      <c r="O207" t="s">
-        <v>666</v>
-      </c>
-      <c r="Q207" t="s">
-        <v>680</v>
-      </c>
-      <c r="R207" t="s">
-        <v>680</v>
-      </c>
-      <c r="T207" t="s">
+      <c r="I227" t="s">
+        <v>25</v>
+      </c>
+      <c r="J227" t="s">
+        <v>26</v>
+      </c>
+      <c r="K227" t="s">
+        <v>27</v>
+      </c>
+      <c r="M227" t="s">
+        <v>28</v>
+      </c>
+      <c r="N227" t="s">
+        <v>744</v>
+      </c>
+      <c r="O227" t="s">
+        <v>728</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>742</v>
+      </c>
+      <c r="R227" t="s">
+        <v>742</v>
+      </c>
+      <c r="T227" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U207" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U227" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>